--- a/Lesson-03/Sales_Commission_Analysis.xlsx
+++ b/Lesson-03/Sales_Commission_Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Excel_Data_Analyst_Journey\Lesson-03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516F5250-8D1D-4D6C-8E84-D0ED1F6D2195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A322FC-F4E2-4088-80BB-350FC4DDCD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -265,10 +265,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="_-[$₦-46A]* #,##0.00_-;\-[$₦-46A]* #,##0.00_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
-    <numFmt numFmtId="172" formatCode="0.0"/>
-    <numFmt numFmtId="174" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -340,7 +340,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -399,8 +399,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -418,23 +417,23 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -442,240 +441,8 @@
   </cellStyles>
   <dxfs count="24">
     <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <numFmt numFmtId="167" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;_-;_-@_-"/>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="180" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="_-[$₦-46A]* #,##0.00_-;\-[$₦-46A]* #,##0.00_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="180" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="180" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="180" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="174" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="180" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="180" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -796,6 +563,238 @@
         <charset val="1"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="_-[$₦-46A]* #,##0.00_-;\-[$₦-46A]* #,##0.00_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="_-[$₦-46A]* #,##0_-;\-[$₦-46A]* #,##0_-;_-[$₦-46A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -834,11 +833,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3E0371C-334E-4F61-BA3D-8D1FDA1E1429}" name="SalesData" displayName="SalesData" ref="A1:E101" totalsRowShown="0">
   <autoFilter ref="A1:E101" xr:uid="{F3E0371C-334E-4F61-BA3D-8D1FDA1E1429}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2A023005-DA62-4905-8CB9-B3659DA5C55A}" name="Salesperson" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{B7E99B0C-87CF-47A6-8B4D-BDAB54EFC0E5}" name="Region" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{BE6431A8-EB74-4E55-9116-D371EA25A103}" name="Sales" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{124967CB-ABCF-4621-9878-774E948A1399}" name="Target" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{D102C746-B91B-4CD2-85B3-A00CC77D4011}" name="Target_Achievement" dataDxfId="7" dataCellStyle="Percent">
+    <tableColumn id="1" xr3:uid="{2A023005-DA62-4905-8CB9-B3659DA5C55A}" name="Salesperson" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{B7E99B0C-87CF-47A6-8B4D-BDAB54EFC0E5}" name="Region" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{BE6431A8-EB74-4E55-9116-D371EA25A103}" name="Sales" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{124967CB-ABCF-4621-9878-774E948A1399}" name="Target" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{D102C746-B91B-4CD2-85B3-A00CC77D4011}" name="Target_Achievement" dataDxfId="12" dataCellStyle="Percent">
       <calculatedColumnFormula>SalesData[[#This Row],[Sales]]/SalesData[[#This Row],[Target]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -850,11 +849,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B30AD900-8979-4638-91FE-9DF20ABE81C0}" name="Table2" displayName="Table2" ref="A1:E101" totalsRowShown="0">
   <autoFilter ref="A1:E101" xr:uid="{B30AD900-8979-4638-91FE-9DF20ABE81C0}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{6DFBC007-9A75-4317-B656-4B2D52557468}" name="Salesperson" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{39A35324-AD3E-4890-A881-03DCB07E00C2}" name="Region" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{4D6409FA-E629-42AA-915A-199CEDB6D9E5}" name="Sales" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{503FD2EF-939E-422D-AE1D-BE1B8FFBD9AD}" name="Target" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{B881C244-4105-4CAF-AD26-927BB845FAE4}" name="Commission" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{6DFBC007-9A75-4317-B656-4B2D52557468}" name="Salesperson" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{39A35324-AD3E-4890-A881-03DCB07E00C2}" name="Region" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{4D6409FA-E629-42AA-915A-199CEDB6D9E5}" name="Sales" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{503FD2EF-939E-422D-AE1D-BE1B8FFBD9AD}" name="Target" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{B881C244-4105-4CAF-AD26-927BB845FAE4}" name="Commission" dataDxfId="7">
       <calculatedColumnFormula>Table2[[#This Row],[Sales]]*$G$2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -866,15 +865,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8EC9266F-C689-4999-BCB8-ED5356D5CF41}" name="Table3" displayName="Table3" ref="A1:F101" totalsRowShown="0">
   <autoFilter ref="A1:F101" xr:uid="{8EC9266F-C689-4999-BCB8-ED5356D5CF41}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{50A42E6D-F5B2-46EA-A031-348C3BA2E398}" name="Salesperson" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{7AA2E647-F194-4568-BFA3-328221F72544}" name="Region" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{F2960502-F8D3-412F-9A5D-C0F56EE08D18}" name="Sales" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{EDC7DFA2-6DF6-4C67-881A-62D7A93919DD}" name="Target" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{198AF868-67A9-497A-B8F6-405E7DD8A52A}" name="Target_Achievement" dataDxfId="17" dataCellStyle="Percent">
+    <tableColumn id="1" xr3:uid="{50A42E6D-F5B2-46EA-A031-348C3BA2E398}" name="Salesperson" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{7AA2E647-F194-4568-BFA3-328221F72544}" name="Region" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{F2960502-F8D3-412F-9A5D-C0F56EE08D18}" name="Sales" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{EDC7DFA2-6DF6-4C67-881A-62D7A93919DD}" name="Target" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{198AF868-67A9-497A-B8F6-405E7DD8A52A}" name="Target_Achievement" dataDxfId="2" dataCellStyle="Percent">
       <calculatedColumnFormula>Table3[[#This Row],[Sales]]/Table3[[#This Row],[Target]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FCA14CEE-29DE-4F6B-8977-7E8ED3C8F00E}" name="Performance_Status" dataDxfId="16">
-      <calculatedColumnFormula>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{FCA14CEE-29DE-4F6B-8977-7E8ED3C8F00E}" name="Performance_Status" dataDxfId="1">
+      <calculatedColumnFormula>IF(E2&lt;100%,"Below Target",IF(E2=100%,"Target Achieved","Above Target"))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -885,21 +884,21 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{33699D96-387E-43D2-BDBC-D5E8734C79AA}" name="Table5" displayName="Table5" ref="A1:H101" totalsRowShown="0">
   <autoFilter ref="A1:H101" xr:uid="{33699D96-387E-43D2-BDBC-D5E8734C79AA}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{056DF319-3A9D-448E-B517-9D1DEDBED29F}" name="Salesperson" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{3EAC8FC5-FEAB-4A34-BEFD-C1156656C4C9}" name="Region" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{5634DE40-36D6-4D8B-B96A-CC757DD17488}" name="Sales" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{A1FD961C-122F-4A7A-A199-44EFF4A54D48}" name="Target" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{8CA3B1EF-ABF1-4DB7-97D3-6D6553619568}" name="Target_Achievement" dataDxfId="12" dataCellStyle="Percent">
+    <tableColumn id="1" xr3:uid="{056DF319-3A9D-448E-B517-9D1DEDBED29F}" name="Salesperson" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{3EAC8FC5-FEAB-4A34-BEFD-C1156656C4C9}" name="Region" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{5634DE40-36D6-4D8B-B96A-CC757DD17488}" name="Sales" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{A1FD961C-122F-4A7A-A199-44EFF4A54D48}" name="Target" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{8CA3B1EF-ABF1-4DB7-97D3-6D6553619568}" name="Target_Achievement" dataDxfId="19" dataCellStyle="Percent">
       <calculatedColumnFormula>Table5[[#This Row],[Sales]]/Table5[[#This Row],[Target]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{27C01CD7-63D3-4531-A3BD-E1485A688E41}" name="Performance_Status" dataDxfId="0" dataCellStyle="Percent">
+    <tableColumn id="6" xr3:uid="{27C01CD7-63D3-4531-A3BD-E1485A688E41}" name="Performance_Status" dataDxfId="18" dataCellStyle="Percent">
       <calculatedColumnFormula>IF(E2&lt;100%,"Below Target",IF(E2=100%,"Target Achieved","Above Target"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{DF793379-47BF-4B75-B680-976CF441B4BC}" name="Multiplier" dataDxfId="1" dataCellStyle="Percent">
+    <tableColumn id="7" xr3:uid="{DF793379-47BF-4B75-B680-976CF441B4BC}" name="Multiplier" dataDxfId="17" dataCellStyle="Percent">
       <calculatedColumnFormula>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{922B5646-770F-4B60-9ABF-6E53FA3EE306}" name="Commission" dataDxfId="10" dataCellStyle="Percent">
-      <calculatedColumnFormula>Table5[[#This Row],[Sales]]*$K$2</calculatedColumnFormula>
+    <tableColumn id="8" xr3:uid="{922B5646-770F-4B60-9ABF-6E53FA3EE306}" name="Commission" dataDxfId="0" dataCellStyle="Percent">
+      <calculatedColumnFormula>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2519,7 +2518,7 @@
   <cols>
     <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.140625" style="34" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.85546875" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2530,10 +2529,10 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="32" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
@@ -2547,10 +2546,10 @@
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="34">
+      <c r="C2" s="33">
         <v>800000</v>
       </c>
-      <c r="D2" s="34">
+      <c r="D2" s="33">
         <v>700000</v>
       </c>
       <c r="E2" s="6">
@@ -2565,10 +2564,10 @@
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="33">
         <v>910000</v>
       </c>
-      <c r="D3" s="34">
+      <c r="D3" s="33">
         <v>800000</v>
       </c>
       <c r="E3" s="6">
@@ -2583,10 +2582,10 @@
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="33">
         <v>770000</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="33">
         <v>750000</v>
       </c>
       <c r="E4" s="6">
@@ -2601,10 +2600,10 @@
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="33">
         <v>540000</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="33">
         <v>750000</v>
       </c>
       <c r="E5" s="6">
@@ -2619,10 +2618,10 @@
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="33">
         <v>780000</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="33">
         <v>1100000</v>
       </c>
       <c r="E6" s="6">
@@ -2637,10 +2636,10 @@
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="33">
         <v>730000</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="33">
         <v>1000000</v>
       </c>
       <c r="E7" s="6">
@@ -2655,10 +2654,10 @@
       <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="33">
         <v>1620000</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="33">
         <v>1300000</v>
       </c>
       <c r="E8" s="6">
@@ -2673,10 +2672,10 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="33">
         <v>1110000</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="33">
         <v>1250000</v>
       </c>
       <c r="E9" s="6">
@@ -2691,10 +2690,10 @@
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="33">
         <v>1120000</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>850000</v>
       </c>
       <c r="E10" s="6">
@@ -2709,10 +2708,10 @@
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="33">
         <v>640000</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="33">
         <v>750000</v>
       </c>
       <c r="E11" s="6">
@@ -2727,10 +2726,10 @@
       <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="33">
         <v>880000</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="33">
         <v>1150000</v>
       </c>
       <c r="E12" s="6">
@@ -2745,10 +2744,10 @@
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="33">
         <v>710000</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="33">
         <v>1100000</v>
       </c>
       <c r="E13" s="6">
@@ -2763,10 +2762,10 @@
       <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="33">
         <v>740000</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="33">
         <v>750000</v>
       </c>
       <c r="E14" s="6">
@@ -2781,10 +2780,10 @@
       <c r="B15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="33">
         <v>810000</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="33">
         <v>1150000</v>
       </c>
       <c r="E15" s="6">
@@ -2799,10 +2798,10 @@
       <c r="B16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="33">
         <v>880000</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="33">
         <v>1200000</v>
       </c>
       <c r="E16" s="6">
@@ -2817,10 +2816,10 @@
       <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="33">
         <v>990000</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="33">
         <v>1350000</v>
       </c>
       <c r="E17" s="6">
@@ -2835,10 +2834,10 @@
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="33">
         <v>820000</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="33">
         <v>900000</v>
       </c>
       <c r="E18" s="6">
@@ -2853,10 +2852,10 @@
       <c r="B19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="33">
         <v>680000</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="33">
         <v>800000</v>
       </c>
       <c r="E19" s="6">
@@ -2871,10 +2870,10 @@
       <c r="B20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="33">
         <v>1620000</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="33">
         <v>1250000</v>
       </c>
       <c r="E20" s="6">
@@ -2889,10 +2888,10 @@
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="33">
         <v>1220000</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="33">
         <v>1150000</v>
       </c>
       <c r="E21" s="6">
@@ -2907,10 +2906,10 @@
       <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="33">
         <v>740000</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="33">
         <v>800000</v>
       </c>
       <c r="E22" s="6">
@@ -2925,10 +2924,10 @@
       <c r="B23" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="33">
         <v>930000</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="33">
         <v>850000</v>
       </c>
       <c r="E23" s="6">
@@ -2943,10 +2942,10 @@
       <c r="B24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="33">
         <v>1030000</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="33">
         <v>850000</v>
       </c>
       <c r="E24" s="6">
@@ -2961,10 +2960,10 @@
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="33">
         <v>760000</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="33">
         <v>1000000</v>
       </c>
       <c r="E25" s="6">
@@ -2979,10 +2978,10 @@
       <c r="B26" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="33">
         <v>910000</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="33">
         <v>850000</v>
       </c>
       <c r="E26" s="6">
@@ -2997,10 +2996,10 @@
       <c r="B27" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="33">
         <v>610000</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="33">
         <v>800000</v>
       </c>
       <c r="E27" s="6">
@@ -3015,10 +3014,10 @@
       <c r="B28" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="33">
         <v>840000</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="33">
         <v>1100000</v>
       </c>
       <c r="E28" s="6">
@@ -3033,10 +3032,10 @@
       <c r="B29" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="33">
         <v>1420000</v>
       </c>
-      <c r="D29" s="34">
+      <c r="D29" s="33">
         <v>1400000</v>
       </c>
       <c r="E29" s="6">
@@ -3051,10 +3050,10 @@
       <c r="B30" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="33">
         <v>770000</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="33">
         <v>800000</v>
       </c>
       <c r="E30" s="6">
@@ -3069,10 +3068,10 @@
       <c r="B31" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="33">
         <v>860000</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="33">
         <v>1350000</v>
       </c>
       <c r="E31" s="6">
@@ -3087,10 +3086,10 @@
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="34">
+      <c r="C32" s="33">
         <v>1420000</v>
       </c>
-      <c r="D32" s="34">
+      <c r="D32" s="33">
         <v>1300000</v>
       </c>
       <c r="E32" s="6">
@@ -3105,10 +3104,10 @@
       <c r="B33" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="33">
         <v>860000</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="33">
         <v>1000000</v>
       </c>
       <c r="E33" s="6">
@@ -3123,10 +3122,10 @@
       <c r="B34" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="33">
         <v>1190000</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="33">
         <v>900000</v>
       </c>
       <c r="E34" s="6">
@@ -3141,10 +3140,10 @@
       <c r="B35" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="33">
         <v>1350000</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="33">
         <v>1200000</v>
       </c>
       <c r="E35" s="6">
@@ -3159,10 +3158,10 @@
       <c r="B36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="33">
         <v>990000</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="33">
         <v>1300000</v>
       </c>
       <c r="E36" s="6">
@@ -3177,10 +3176,10 @@
       <c r="B37" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="34">
+      <c r="C37" s="33">
         <v>590000</v>
       </c>
-      <c r="D37" s="34">
+      <c r="D37" s="33">
         <v>750000</v>
       </c>
       <c r="E37" s="6">
@@ -3195,10 +3194,10 @@
       <c r="B38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="33">
         <v>920000</v>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="33">
         <v>700000</v>
       </c>
       <c r="E38" s="6">
@@ -3213,10 +3212,10 @@
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="34">
+      <c r="C39" s="33">
         <v>1280000</v>
       </c>
-      <c r="D39" s="34">
+      <c r="D39" s="33">
         <v>1100000</v>
       </c>
       <c r="E39" s="6">
@@ -3231,10 +3230,10 @@
       <c r="B40" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="34">
+      <c r="C40" s="33">
         <v>1420000</v>
       </c>
-      <c r="D40" s="34">
+      <c r="D40" s="33">
         <v>1350000</v>
       </c>
       <c r="E40" s="6">
@@ -3249,10 +3248,10 @@
       <c r="B41" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="34">
+      <c r="C41" s="33">
         <v>820000</v>
       </c>
-      <c r="D41" s="34">
+      <c r="D41" s="33">
         <v>1150000</v>
       </c>
       <c r="E41" s="6">
@@ -3267,10 +3266,10 @@
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="34">
+      <c r="C42" s="33">
         <v>1440000</v>
       </c>
-      <c r="D42" s="34">
+      <c r="D42" s="33">
         <v>1100000</v>
       </c>
       <c r="E42" s="6">
@@ -3285,10 +3284,10 @@
       <c r="B43" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="33">
         <v>770000</v>
       </c>
-      <c r="D43" s="34">
+      <c r="D43" s="33">
         <v>1400000</v>
       </c>
       <c r="E43" s="6">
@@ -3303,10 +3302,10 @@
       <c r="B44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="34">
+      <c r="C44" s="33">
         <v>450000</v>
       </c>
-      <c r="D44" s="34">
+      <c r="D44" s="33">
         <v>700000</v>
       </c>
       <c r="E44" s="6">
@@ -3321,10 +3320,10 @@
       <c r="B45" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="34">
+      <c r="C45" s="33">
         <v>510000</v>
       </c>
-      <c r="D45" s="34">
+      <c r="D45" s="33">
         <v>850000</v>
       </c>
       <c r="E45" s="6">
@@ -3339,10 +3338,10 @@
       <c r="B46" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C46" s="34">
+      <c r="C46" s="33">
         <v>850000</v>
       </c>
-      <c r="D46" s="34">
+      <c r="D46" s="33">
         <v>750000</v>
       </c>
       <c r="E46" s="6">
@@ -3357,10 +3356,10 @@
       <c r="B47" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C47" s="34">
+      <c r="C47" s="33">
         <v>1270000</v>
       </c>
-      <c r="D47" s="34">
+      <c r="D47" s="33">
         <v>1300000</v>
       </c>
       <c r="E47" s="6">
@@ -3375,10 +3374,10 @@
       <c r="B48" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="34">
+      <c r="C48" s="33">
         <v>1120000</v>
       </c>
-      <c r="D48" s="34">
+      <c r="D48" s="33">
         <v>1200000</v>
       </c>
       <c r="E48" s="6">
@@ -3393,10 +3392,10 @@
       <c r="B49" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="34">
+      <c r="C49" s="33">
         <v>870000</v>
       </c>
-      <c r="D49" s="34">
+      <c r="D49" s="33">
         <v>900000</v>
       </c>
       <c r="E49" s="6">
@@ -3411,10 +3410,10 @@
       <c r="B50" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C50" s="34">
+      <c r="C50" s="33">
         <v>1100000</v>
       </c>
-      <c r="D50" s="34">
+      <c r="D50" s="33">
         <v>850000</v>
       </c>
       <c r="E50" s="6">
@@ -3429,10 +3428,10 @@
       <c r="B51" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C51" s="34">
+      <c r="C51" s="33">
         <v>1000000</v>
       </c>
-      <c r="D51" s="34">
+      <c r="D51" s="33">
         <v>1250000</v>
       </c>
       <c r="E51" s="6">
@@ -3447,10 +3446,10 @@
       <c r="B52" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C52" s="34">
+      <c r="C52" s="33">
         <v>1330000</v>
       </c>
-      <c r="D52" s="34">
+      <c r="D52" s="33">
         <v>1050000</v>
       </c>
       <c r="E52" s="6">
@@ -3465,10 +3464,10 @@
       <c r="B53" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C53" s="34">
+      <c r="C53" s="33">
         <v>620000</v>
       </c>
-      <c r="D53" s="34">
+      <c r="D53" s="33">
         <v>850000</v>
       </c>
       <c r="E53" s="6">
@@ -3483,10 +3482,10 @@
       <c r="B54" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C54" s="34">
+      <c r="C54" s="33">
         <v>1140000</v>
       </c>
-      <c r="D54" s="34">
+      <c r="D54" s="33">
         <v>1150000</v>
       </c>
       <c r="E54" s="6">
@@ -3501,10 +3500,10 @@
       <c r="B55" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C55" s="34">
+      <c r="C55" s="33">
         <v>420000</v>
       </c>
-      <c r="D55" s="34">
+      <c r="D55" s="33">
         <v>700000</v>
       </c>
       <c r="E55" s="6">
@@ -3519,10 +3518,10 @@
       <c r="B56" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C56" s="34">
+      <c r="C56" s="33">
         <v>510000</v>
       </c>
-      <c r="D56" s="34">
+      <c r="D56" s="33">
         <v>850000</v>
       </c>
       <c r="E56" s="6">
@@ -3537,10 +3536,10 @@
       <c r="B57" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C57" s="34">
+      <c r="C57" s="33">
         <v>720000</v>
       </c>
-      <c r="D57" s="34">
+      <c r="D57" s="33">
         <v>750000</v>
       </c>
       <c r="E57" s="6">
@@ -3555,10 +3554,10 @@
       <c r="B58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C58" s="34">
+      <c r="C58" s="33">
         <v>830000</v>
       </c>
-      <c r="D58" s="34">
+      <c r="D58" s="33">
         <v>850000</v>
       </c>
       <c r="E58" s="6">
@@ -3573,10 +3572,10 @@
       <c r="B59" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C59" s="34">
+      <c r="C59" s="33">
         <v>1000000</v>
       </c>
-      <c r="D59" s="34">
+      <c r="D59" s="33">
         <v>850000</v>
       </c>
       <c r="E59" s="6">
@@ -3591,10 +3590,10 @@
       <c r="B60" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C60" s="34">
+      <c r="C60" s="33">
         <v>530000</v>
       </c>
-      <c r="D60" s="34">
+      <c r="D60" s="33">
         <v>850000</v>
       </c>
       <c r="E60" s="6">
@@ -3609,10 +3608,10 @@
       <c r="B61" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C61" s="34">
+      <c r="C61" s="33">
         <v>840000</v>
       </c>
-      <c r="D61" s="34">
+      <c r="D61" s="33">
         <v>950000</v>
       </c>
       <c r="E61" s="6">
@@ -3627,10 +3626,10 @@
       <c r="B62" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C62" s="34">
+      <c r="C62" s="33">
         <v>1290000</v>
       </c>
-      <c r="D62" s="34">
+      <c r="D62" s="33">
         <v>1200000</v>
       </c>
       <c r="E62" s="6">
@@ -3645,10 +3644,10 @@
       <c r="B63" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C63" s="34">
+      <c r="C63" s="33">
         <v>610000</v>
       </c>
-      <c r="D63" s="34">
+      <c r="D63" s="33">
         <v>700000</v>
       </c>
       <c r="E63" s="6">
@@ -3663,10 +3662,10 @@
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="34">
+      <c r="C64" s="33">
         <v>600000</v>
       </c>
-      <c r="D64" s="34">
+      <c r="D64" s="33">
         <v>850000</v>
       </c>
       <c r="E64" s="6">
@@ -3681,10 +3680,10 @@
       <c r="B65" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C65" s="34">
+      <c r="C65" s="33">
         <v>710000</v>
       </c>
-      <c r="D65" s="34">
+      <c r="D65" s="33">
         <v>800000</v>
       </c>
       <c r="E65" s="6">
@@ -3699,10 +3698,10 @@
       <c r="B66" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="34">
+      <c r="C66" s="33">
         <v>1060000</v>
       </c>
-      <c r="D66" s="34">
+      <c r="D66" s="33">
         <v>850000</v>
       </c>
       <c r="E66" s="6">
@@ -3717,10 +3716,10 @@
       <c r="B67" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C67" s="34">
+      <c r="C67" s="33">
         <v>1610000</v>
       </c>
-      <c r="D67" s="34">
+      <c r="D67" s="33">
         <v>1300000</v>
       </c>
       <c r="E67" s="6">
@@ -3735,10 +3734,10 @@
       <c r="B68" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C68" s="34">
+      <c r="C68" s="33">
         <v>750000</v>
       </c>
-      <c r="D68" s="34">
+      <c r="D68" s="33">
         <v>700000</v>
       </c>
       <c r="E68" s="6">
@@ -3753,10 +3752,10 @@
       <c r="B69" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C69" s="34">
+      <c r="C69" s="33">
         <v>970000</v>
       </c>
-      <c r="D69" s="34">
+      <c r="D69" s="33">
         <v>750000</v>
       </c>
       <c r="E69" s="6">
@@ -3771,10 +3770,10 @@
       <c r="B70" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C70" s="34">
+      <c r="C70" s="33">
         <v>700000</v>
       </c>
-      <c r="D70" s="34">
+      <c r="D70" s="33">
         <v>800000</v>
       </c>
       <c r="E70" s="6">
@@ -3789,10 +3788,10 @@
       <c r="B71" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C71" s="34">
+      <c r="C71" s="33">
         <v>1180000</v>
       </c>
-      <c r="D71" s="34">
+      <c r="D71" s="33">
         <v>1350000</v>
       </c>
       <c r="E71" s="6">
@@ -3807,10 +3806,10 @@
       <c r="B72" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C72" s="34">
+      <c r="C72" s="33">
         <v>550000</v>
       </c>
-      <c r="D72" s="34">
+      <c r="D72" s="33">
         <v>1000000</v>
       </c>
       <c r="E72" s="6">
@@ -3825,10 +3824,10 @@
       <c r="B73" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C73" s="34">
+      <c r="C73" s="33">
         <v>1650000</v>
       </c>
-      <c r="D73" s="34">
+      <c r="D73" s="33">
         <v>1400000</v>
       </c>
       <c r="E73" s="6">
@@ -3843,10 +3842,10 @@
       <c r="B74" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C74" s="34">
+      <c r="C74" s="33">
         <v>1110000</v>
       </c>
-      <c r="D74" s="34">
+      <c r="D74" s="33">
         <v>1000000</v>
       </c>
       <c r="E74" s="6">
@@ -3861,10 +3860,10 @@
       <c r="B75" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C75" s="34">
+      <c r="C75" s="33">
         <v>1350000</v>
       </c>
-      <c r="D75" s="34">
+      <c r="D75" s="33">
         <v>1200000</v>
       </c>
       <c r="E75" s="6">
@@ -3879,10 +3878,10 @@
       <c r="B76" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C76" s="34">
+      <c r="C76" s="33">
         <v>650000</v>
       </c>
-      <c r="D76" s="34">
+      <c r="D76" s="33">
         <v>900000</v>
       </c>
       <c r="E76" s="6">
@@ -3897,10 +3896,10 @@
       <c r="B77" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C77" s="34">
+      <c r="C77" s="33">
         <v>800000</v>
       </c>
-      <c r="D77" s="34">
+      <c r="D77" s="33">
         <v>700000</v>
       </c>
       <c r="E77" s="6">
@@ -3915,10 +3914,10 @@
       <c r="B78" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C78" s="34">
+      <c r="C78" s="33">
         <v>1070000</v>
       </c>
-      <c r="D78" s="34">
+      <c r="D78" s="33">
         <v>1150000</v>
       </c>
       <c r="E78" s="6">
@@ -3933,10 +3932,10 @@
       <c r="B79" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C79" s="34">
+      <c r="C79" s="33">
         <v>480000</v>
       </c>
-      <c r="D79" s="34">
+      <c r="D79" s="33">
         <v>800000</v>
       </c>
       <c r="E79" s="6">
@@ -3951,10 +3950,10 @@
       <c r="B80" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C80" s="34">
+      <c r="C80" s="33">
         <v>940000</v>
       </c>
-      <c r="D80" s="34">
+      <c r="D80" s="33">
         <v>1350000</v>
       </c>
       <c r="E80" s="6">
@@ -3969,10 +3968,10 @@
       <c r="B81" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C81" s="34">
+      <c r="C81" s="33">
         <v>1490000</v>
       </c>
-      <c r="D81" s="34">
+      <c r="D81" s="33">
         <v>1200000</v>
       </c>
       <c r="E81" s="6">
@@ -3987,10 +3986,10 @@
       <c r="B82" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="34">
+      <c r="C82" s="33">
         <v>1410000</v>
       </c>
-      <c r="D82" s="34">
+      <c r="D82" s="33">
         <v>1400000</v>
       </c>
       <c r="E82" s="6">
@@ -4005,10 +4004,10 @@
       <c r="B83" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C83" s="34">
+      <c r="C83" s="33">
         <v>710000</v>
       </c>
-      <c r="D83" s="34">
+      <c r="D83" s="33">
         <v>1150000</v>
       </c>
       <c r="E83" s="6">
@@ -4023,10 +4022,10 @@
       <c r="B84" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C84" s="34">
+      <c r="C84" s="33">
         <v>1230000</v>
       </c>
-      <c r="D84" s="34">
+      <c r="D84" s="33">
         <v>950000</v>
       </c>
       <c r="E84" s="6">
@@ -4041,10 +4040,10 @@
       <c r="B85" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C85" s="34">
+      <c r="C85" s="33">
         <v>650000</v>
       </c>
-      <c r="D85" s="34">
+      <c r="D85" s="33">
         <v>850000</v>
       </c>
       <c r="E85" s="6">
@@ -4059,10 +4058,10 @@
       <c r="B86" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C86" s="34">
+      <c r="C86" s="33">
         <v>840000</v>
       </c>
-      <c r="D86" s="34">
+      <c r="D86" s="33">
         <v>1050000</v>
       </c>
       <c r="E86" s="6">
@@ -4077,10 +4076,10 @@
       <c r="B87" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C87" s="34">
+      <c r="C87" s="33">
         <v>640000</v>
       </c>
-      <c r="D87" s="34">
+      <c r="D87" s="33">
         <v>700000</v>
       </c>
       <c r="E87" s="6">
@@ -4095,10 +4094,10 @@
       <c r="B88" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C88" s="34">
+      <c r="C88" s="33">
         <v>740000</v>
       </c>
-      <c r="D88" s="34">
+      <c r="D88" s="33">
         <v>750000</v>
       </c>
       <c r="E88" s="6">
@@ -4113,10 +4112,10 @@
       <c r="B89" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C89" s="34">
+      <c r="C89" s="33">
         <v>1040000</v>
       </c>
-      <c r="D89" s="34">
+      <c r="D89" s="33">
         <v>800000</v>
       </c>
       <c r="E89" s="6">
@@ -4131,10 +4130,10 @@
       <c r="B90" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C90" s="34">
+      <c r="C90" s="33">
         <v>1040000</v>
       </c>
-      <c r="D90" s="34">
+      <c r="D90" s="33">
         <v>1400000</v>
       </c>
       <c r="E90" s="6">
@@ -4149,10 +4148,10 @@
       <c r="B91" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C91" s="34">
+      <c r="C91" s="33">
         <v>1280000</v>
       </c>
-      <c r="D91" s="34">
+      <c r="D91" s="33">
         <v>1050000</v>
       </c>
       <c r="E91" s="6">
@@ -4167,10 +4166,10 @@
       <c r="B92" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C92" s="34">
+      <c r="C92" s="33">
         <v>1540000</v>
       </c>
-      <c r="D92" s="34">
+      <c r="D92" s="33">
         <v>1150000</v>
       </c>
       <c r="E92" s="6">
@@ -4185,10 +4184,10 @@
       <c r="B93" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C93" s="34">
+      <c r="C93" s="33">
         <v>760000</v>
       </c>
-      <c r="D93" s="34">
+      <c r="D93" s="33">
         <v>700000</v>
       </c>
       <c r="E93" s="6">
@@ -4203,10 +4202,10 @@
       <c r="B94" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C94" s="34">
+      <c r="C94" s="33">
         <v>1510000</v>
       </c>
-      <c r="D94" s="34">
+      <c r="D94" s="33">
         <v>1400000</v>
       </c>
       <c r="E94" s="6">
@@ -4221,10 +4220,10 @@
       <c r="B95" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C95" s="34">
+      <c r="C95" s="33">
         <v>580000</v>
       </c>
-      <c r="D95" s="34">
+      <c r="D95" s="33">
         <v>900000</v>
       </c>
       <c r="E95" s="6">
@@ -4239,10 +4238,10 @@
       <c r="B96" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C96" s="34">
+      <c r="C96" s="33">
         <v>610000</v>
       </c>
-      <c r="D96" s="34">
+      <c r="D96" s="33">
         <v>800000</v>
       </c>
       <c r="E96" s="6">
@@ -4257,10 +4256,10 @@
       <c r="B97" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C97" s="34">
+      <c r="C97" s="33">
         <v>1030000</v>
       </c>
-      <c r="D97" s="34">
+      <c r="D97" s="33">
         <v>1250000</v>
       </c>
       <c r="E97" s="6">
@@ -4275,10 +4274,10 @@
       <c r="B98" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C98" s="34">
+      <c r="C98" s="33">
         <v>1030000</v>
       </c>
-      <c r="D98" s="34">
+      <c r="D98" s="33">
         <v>1100000</v>
       </c>
       <c r="E98" s="6">
@@ -4293,10 +4292,10 @@
       <c r="B99" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C99" s="34">
+      <c r="C99" s="33">
         <v>790000</v>
       </c>
-      <c r="D99" s="34">
+      <c r="D99" s="33">
         <v>750000</v>
       </c>
       <c r="E99" s="6">
@@ -4311,10 +4310,10 @@
       <c r="B100" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C100" s="34">
+      <c r="C100" s="33">
         <v>390000</v>
       </c>
-      <c r="D100" s="34">
+      <c r="D100" s="33">
         <v>700000</v>
       </c>
       <c r="E100" s="6">
@@ -4329,10 +4328,10 @@
       <c r="B101" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C101" s="34">
+      <c r="C101" s="33">
         <v>1600000</v>
       </c>
-      <c r="D101" s="34">
+      <c r="D101" s="33">
         <v>1200000</v>
       </c>
       <c r="E101" s="6">
@@ -4355,7 +4354,7 @@
   <cols>
     <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.140625" style="34" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -4367,10 +4366,10 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="32" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="13" t="s">
@@ -4387,10 +4386,10 @@
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="34">
+      <c r="C2" s="33">
         <v>800000</v>
       </c>
-      <c r="D2" s="34">
+      <c r="D2" s="33">
         <v>700000</v>
       </c>
       <c r="E2" s="12">
@@ -4408,10 +4407,10 @@
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="33">
         <v>910000</v>
       </c>
-      <c r="D3" s="34">
+      <c r="D3" s="33">
         <v>800000</v>
       </c>
       <c r="E3" s="12">
@@ -4426,10 +4425,10 @@
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="33">
         <v>770000</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="33">
         <v>750000</v>
       </c>
       <c r="E4" s="12">
@@ -4444,10 +4443,10 @@
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="33">
         <v>540000</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="33">
         <v>750000</v>
       </c>
       <c r="E5" s="12">
@@ -4462,10 +4461,10 @@
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="33">
         <v>780000</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="33">
         <v>1100000</v>
       </c>
       <c r="E6" s="12">
@@ -4480,10 +4479,10 @@
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="33">
         <v>730000</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="33">
         <v>1000000</v>
       </c>
       <c r="E7" s="12">
@@ -4498,10 +4497,10 @@
       <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="33">
         <v>1620000</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="33">
         <v>1300000</v>
       </c>
       <c r="E8" s="12">
@@ -4516,10 +4515,10 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="33">
         <v>1110000</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="33">
         <v>1250000</v>
       </c>
       <c r="E9" s="12">
@@ -4534,10 +4533,10 @@
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="33">
         <v>1120000</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>850000</v>
       </c>
       <c r="E10" s="12">
@@ -4552,10 +4551,10 @@
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="33">
         <v>640000</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="33">
         <v>750000</v>
       </c>
       <c r="E11" s="12">
@@ -4570,10 +4569,10 @@
       <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="33">
         <v>880000</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="33">
         <v>1150000</v>
       </c>
       <c r="E12" s="12">
@@ -4588,10 +4587,10 @@
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="33">
         <v>710000</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="33">
         <v>1100000</v>
       </c>
       <c r="E13" s="12">
@@ -4606,10 +4605,10 @@
       <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="33">
         <v>740000</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="33">
         <v>750000</v>
       </c>
       <c r="E14" s="12">
@@ -4624,10 +4623,10 @@
       <c r="B15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="33">
         <v>810000</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="33">
         <v>1150000</v>
       </c>
       <c r="E15" s="12">
@@ -4642,10 +4641,10 @@
       <c r="B16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="33">
         <v>880000</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="33">
         <v>1200000</v>
       </c>
       <c r="E16" s="12">
@@ -4660,10 +4659,10 @@
       <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="33">
         <v>990000</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="33">
         <v>1350000</v>
       </c>
       <c r="E17" s="12">
@@ -4678,10 +4677,10 @@
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="33">
         <v>820000</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="33">
         <v>900000</v>
       </c>
       <c r="E18" s="12">
@@ -4696,10 +4695,10 @@
       <c r="B19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="33">
         <v>680000</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="33">
         <v>800000</v>
       </c>
       <c r="E19" s="12">
@@ -4714,10 +4713,10 @@
       <c r="B20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="33">
         <v>1620000</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="33">
         <v>1250000</v>
       </c>
       <c r="E20" s="12">
@@ -4732,10 +4731,10 @@
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="33">
         <v>1220000</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="33">
         <v>1150000</v>
       </c>
       <c r="E21" s="12">
@@ -4750,10 +4749,10 @@
       <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="33">
         <v>740000</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="33">
         <v>800000</v>
       </c>
       <c r="E22" s="12">
@@ -4768,10 +4767,10 @@
       <c r="B23" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="33">
         <v>930000</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="33">
         <v>850000</v>
       </c>
       <c r="E23" s="12">
@@ -4786,10 +4785,10 @@
       <c r="B24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="33">
         <v>1030000</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="33">
         <v>850000</v>
       </c>
       <c r="E24" s="12">
@@ -4804,10 +4803,10 @@
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="33">
         <v>760000</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="33">
         <v>1000000</v>
       </c>
       <c r="E25" s="12">
@@ -4822,10 +4821,10 @@
       <c r="B26" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="33">
         <v>910000</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="33">
         <v>850000</v>
       </c>
       <c r="E26" s="12">
@@ -4840,10 +4839,10 @@
       <c r="B27" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="33">
         <v>610000</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="33">
         <v>800000</v>
       </c>
       <c r="E27" s="12">
@@ -4858,10 +4857,10 @@
       <c r="B28" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="33">
         <v>840000</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="33">
         <v>1100000</v>
       </c>
       <c r="E28" s="12">
@@ -4876,10 +4875,10 @@
       <c r="B29" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="33">
         <v>1420000</v>
       </c>
-      <c r="D29" s="34">
+      <c r="D29" s="33">
         <v>1400000</v>
       </c>
       <c r="E29" s="12">
@@ -4894,10 +4893,10 @@
       <c r="B30" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="33">
         <v>770000</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="33">
         <v>800000</v>
       </c>
       <c r="E30" s="12">
@@ -4912,10 +4911,10 @@
       <c r="B31" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="33">
         <v>860000</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="33">
         <v>1350000</v>
       </c>
       <c r="E31" s="12">
@@ -4930,10 +4929,10 @@
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="34">
+      <c r="C32" s="33">
         <v>1420000</v>
       </c>
-      <c r="D32" s="34">
+      <c r="D32" s="33">
         <v>1300000</v>
       </c>
       <c r="E32" s="12">
@@ -4948,10 +4947,10 @@
       <c r="B33" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="33">
         <v>860000</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="33">
         <v>1000000</v>
       </c>
       <c r="E33" s="12">
@@ -4966,10 +4965,10 @@
       <c r="B34" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="33">
         <v>1190000</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="33">
         <v>900000</v>
       </c>
       <c r="E34" s="12">
@@ -4984,10 +4983,10 @@
       <c r="B35" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="33">
         <v>1350000</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="33">
         <v>1200000</v>
       </c>
       <c r="E35" s="12">
@@ -5002,10 +5001,10 @@
       <c r="B36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="33">
         <v>990000</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="33">
         <v>1300000</v>
       </c>
       <c r="E36" s="12">
@@ -5020,10 +5019,10 @@
       <c r="B37" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="34">
+      <c r="C37" s="33">
         <v>590000</v>
       </c>
-      <c r="D37" s="34">
+      <c r="D37" s="33">
         <v>750000</v>
       </c>
       <c r="E37" s="12">
@@ -5038,10 +5037,10 @@
       <c r="B38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="33">
         <v>920000</v>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="33">
         <v>700000</v>
       </c>
       <c r="E38" s="12">
@@ -5056,10 +5055,10 @@
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="34">
+      <c r="C39" s="33">
         <v>1280000</v>
       </c>
-      <c r="D39" s="34">
+      <c r="D39" s="33">
         <v>1100000</v>
       </c>
       <c r="E39" s="12">
@@ -5074,10 +5073,10 @@
       <c r="B40" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="34">
+      <c r="C40" s="33">
         <v>1420000</v>
       </c>
-      <c r="D40" s="34">
+      <c r="D40" s="33">
         <v>1350000</v>
       </c>
       <c r="E40" s="12">
@@ -5092,10 +5091,10 @@
       <c r="B41" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="34">
+      <c r="C41" s="33">
         <v>820000</v>
       </c>
-      <c r="D41" s="34">
+      <c r="D41" s="33">
         <v>1150000</v>
       </c>
       <c r="E41" s="12">
@@ -5110,10 +5109,10 @@
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="34">
+      <c r="C42" s="33">
         <v>1440000</v>
       </c>
-      <c r="D42" s="34">
+      <c r="D42" s="33">
         <v>1100000</v>
       </c>
       <c r="E42" s="12">
@@ -5128,10 +5127,10 @@
       <c r="B43" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="33">
         <v>770000</v>
       </c>
-      <c r="D43" s="34">
+      <c r="D43" s="33">
         <v>1400000</v>
       </c>
       <c r="E43" s="12">
@@ -5146,10 +5145,10 @@
       <c r="B44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="34">
+      <c r="C44" s="33">
         <v>450000</v>
       </c>
-      <c r="D44" s="34">
+      <c r="D44" s="33">
         <v>700000</v>
       </c>
       <c r="E44" s="12">
@@ -5164,10 +5163,10 @@
       <c r="B45" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="34">
+      <c r="C45" s="33">
         <v>510000</v>
       </c>
-      <c r="D45" s="34">
+      <c r="D45" s="33">
         <v>850000</v>
       </c>
       <c r="E45" s="12">
@@ -5182,10 +5181,10 @@
       <c r="B46" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C46" s="34">
+      <c r="C46" s="33">
         <v>850000</v>
       </c>
-      <c r="D46" s="34">
+      <c r="D46" s="33">
         <v>750000</v>
       </c>
       <c r="E46" s="12">
@@ -5200,10 +5199,10 @@
       <c r="B47" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C47" s="34">
+      <c r="C47" s="33">
         <v>1270000</v>
       </c>
-      <c r="D47" s="34">
+      <c r="D47" s="33">
         <v>1300000</v>
       </c>
       <c r="E47" s="12">
@@ -5218,10 +5217,10 @@
       <c r="B48" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="34">
+      <c r="C48" s="33">
         <v>1120000</v>
       </c>
-      <c r="D48" s="34">
+      <c r="D48" s="33">
         <v>1200000</v>
       </c>
       <c r="E48" s="12">
@@ -5236,10 +5235,10 @@
       <c r="B49" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="34">
+      <c r="C49" s="33">
         <v>870000</v>
       </c>
-      <c r="D49" s="34">
+      <c r="D49" s="33">
         <v>900000</v>
       </c>
       <c r="E49" s="12">
@@ -5254,10 +5253,10 @@
       <c r="B50" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C50" s="34">
+      <c r="C50" s="33">
         <v>1100000</v>
       </c>
-      <c r="D50" s="34">
+      <c r="D50" s="33">
         <v>850000</v>
       </c>
       <c r="E50" s="12">
@@ -5272,10 +5271,10 @@
       <c r="B51" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C51" s="34">
+      <c r="C51" s="33">
         <v>1000000</v>
       </c>
-      <c r="D51" s="34">
+      <c r="D51" s="33">
         <v>1250000</v>
       </c>
       <c r="E51" s="12">
@@ -5290,10 +5289,10 @@
       <c r="B52" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C52" s="34">
+      <c r="C52" s="33">
         <v>1330000</v>
       </c>
-      <c r="D52" s="34">
+      <c r="D52" s="33">
         <v>1050000</v>
       </c>
       <c r="E52" s="12">
@@ -5308,10 +5307,10 @@
       <c r="B53" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C53" s="34">
+      <c r="C53" s="33">
         <v>620000</v>
       </c>
-      <c r="D53" s="34">
+      <c r="D53" s="33">
         <v>850000</v>
       </c>
       <c r="E53" s="12">
@@ -5326,10 +5325,10 @@
       <c r="B54" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C54" s="34">
+      <c r="C54" s="33">
         <v>1140000</v>
       </c>
-      <c r="D54" s="34">
+      <c r="D54" s="33">
         <v>1150000</v>
       </c>
       <c r="E54" s="12">
@@ -5344,10 +5343,10 @@
       <c r="B55" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C55" s="34">
+      <c r="C55" s="33">
         <v>420000</v>
       </c>
-      <c r="D55" s="34">
+      <c r="D55" s="33">
         <v>700000</v>
       </c>
       <c r="E55" s="12">
@@ -5362,10 +5361,10 @@
       <c r="B56" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C56" s="34">
+      <c r="C56" s="33">
         <v>510000</v>
       </c>
-      <c r="D56" s="34">
+      <c r="D56" s="33">
         <v>850000</v>
       </c>
       <c r="E56" s="12">
@@ -5380,10 +5379,10 @@
       <c r="B57" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C57" s="34">
+      <c r="C57" s="33">
         <v>720000</v>
       </c>
-      <c r="D57" s="34">
+      <c r="D57" s="33">
         <v>750000</v>
       </c>
       <c r="E57" s="12">
@@ -5398,10 +5397,10 @@
       <c r="B58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C58" s="34">
+      <c r="C58" s="33">
         <v>830000</v>
       </c>
-      <c r="D58" s="34">
+      <c r="D58" s="33">
         <v>850000</v>
       </c>
       <c r="E58" s="12">
@@ -5416,10 +5415,10 @@
       <c r="B59" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C59" s="34">
+      <c r="C59" s="33">
         <v>1000000</v>
       </c>
-      <c r="D59" s="34">
+      <c r="D59" s="33">
         <v>850000</v>
       </c>
       <c r="E59" s="12">
@@ -5434,10 +5433,10 @@
       <c r="B60" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C60" s="34">
+      <c r="C60" s="33">
         <v>530000</v>
       </c>
-      <c r="D60" s="34">
+      <c r="D60" s="33">
         <v>850000</v>
       </c>
       <c r="E60" s="12">
@@ -5452,10 +5451,10 @@
       <c r="B61" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C61" s="34">
+      <c r="C61" s="33">
         <v>840000</v>
       </c>
-      <c r="D61" s="34">
+      <c r="D61" s="33">
         <v>950000</v>
       </c>
       <c r="E61" s="12">
@@ -5470,10 +5469,10 @@
       <c r="B62" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C62" s="34">
+      <c r="C62" s="33">
         <v>1290000</v>
       </c>
-      <c r="D62" s="34">
+      <c r="D62" s="33">
         <v>1200000</v>
       </c>
       <c r="E62" s="12">
@@ -5488,10 +5487,10 @@
       <c r="B63" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C63" s="34">
+      <c r="C63" s="33">
         <v>610000</v>
       </c>
-      <c r="D63" s="34">
+      <c r="D63" s="33">
         <v>700000</v>
       </c>
       <c r="E63" s="12">
@@ -5506,10 +5505,10 @@
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="34">
+      <c r="C64" s="33">
         <v>600000</v>
       </c>
-      <c r="D64" s="34">
+      <c r="D64" s="33">
         <v>850000</v>
       </c>
       <c r="E64" s="12">
@@ -5524,10 +5523,10 @@
       <c r="B65" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C65" s="34">
+      <c r="C65" s="33">
         <v>710000</v>
       </c>
-      <c r="D65" s="34">
+      <c r="D65" s="33">
         <v>800000</v>
       </c>
       <c r="E65" s="12">
@@ -5542,10 +5541,10 @@
       <c r="B66" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="34">
+      <c r="C66" s="33">
         <v>1060000</v>
       </c>
-      <c r="D66" s="34">
+      <c r="D66" s="33">
         <v>850000</v>
       </c>
       <c r="E66" s="12">
@@ -5560,10 +5559,10 @@
       <c r="B67" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C67" s="34">
+      <c r="C67" s="33">
         <v>1610000</v>
       </c>
-      <c r="D67" s="34">
+      <c r="D67" s="33">
         <v>1300000</v>
       </c>
       <c r="E67" s="12">
@@ -5578,10 +5577,10 @@
       <c r="B68" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C68" s="34">
+      <c r="C68" s="33">
         <v>750000</v>
       </c>
-      <c r="D68" s="34">
+      <c r="D68" s="33">
         <v>700000</v>
       </c>
       <c r="E68" s="12">
@@ -5596,10 +5595,10 @@
       <c r="B69" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C69" s="34">
+      <c r="C69" s="33">
         <v>970000</v>
       </c>
-      <c r="D69" s="34">
+      <c r="D69" s="33">
         <v>750000</v>
       </c>
       <c r="E69" s="12">
@@ -5614,10 +5613,10 @@
       <c r="B70" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C70" s="34">
+      <c r="C70" s="33">
         <v>700000</v>
       </c>
-      <c r="D70" s="34">
+      <c r="D70" s="33">
         <v>800000</v>
       </c>
       <c r="E70" s="12">
@@ -5632,10 +5631,10 @@
       <c r="B71" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C71" s="34">
+      <c r="C71" s="33">
         <v>1180000</v>
       </c>
-      <c r="D71" s="34">
+      <c r="D71" s="33">
         <v>1350000</v>
       </c>
       <c r="E71" s="12">
@@ -5650,10 +5649,10 @@
       <c r="B72" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C72" s="34">
+      <c r="C72" s="33">
         <v>550000</v>
       </c>
-      <c r="D72" s="34">
+      <c r="D72" s="33">
         <v>1000000</v>
       </c>
       <c r="E72" s="12">
@@ -5668,10 +5667,10 @@
       <c r="B73" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C73" s="34">
+      <c r="C73" s="33">
         <v>1650000</v>
       </c>
-      <c r="D73" s="34">
+      <c r="D73" s="33">
         <v>1400000</v>
       </c>
       <c r="E73" s="12">
@@ -5686,10 +5685,10 @@
       <c r="B74" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C74" s="34">
+      <c r="C74" s="33">
         <v>1110000</v>
       </c>
-      <c r="D74" s="34">
+      <c r="D74" s="33">
         <v>1000000</v>
       </c>
       <c r="E74" s="12">
@@ -5704,10 +5703,10 @@
       <c r="B75" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C75" s="34">
+      <c r="C75" s="33">
         <v>1350000</v>
       </c>
-      <c r="D75" s="34">
+      <c r="D75" s="33">
         <v>1200000</v>
       </c>
       <c r="E75" s="12">
@@ -5722,10 +5721,10 @@
       <c r="B76" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C76" s="34">
+      <c r="C76" s="33">
         <v>650000</v>
       </c>
-      <c r="D76" s="34">
+      <c r="D76" s="33">
         <v>900000</v>
       </c>
       <c r="E76" s="12">
@@ -5740,10 +5739,10 @@
       <c r="B77" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C77" s="34">
+      <c r="C77" s="33">
         <v>800000</v>
       </c>
-      <c r="D77" s="34">
+      <c r="D77" s="33">
         <v>700000</v>
       </c>
       <c r="E77" s="12">
@@ -5758,10 +5757,10 @@
       <c r="B78" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C78" s="34">
+      <c r="C78" s="33">
         <v>1070000</v>
       </c>
-      <c r="D78" s="34">
+      <c r="D78" s="33">
         <v>1150000</v>
       </c>
       <c r="E78" s="12">
@@ -5776,10 +5775,10 @@
       <c r="B79" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C79" s="34">
+      <c r="C79" s="33">
         <v>480000</v>
       </c>
-      <c r="D79" s="34">
+      <c r="D79" s="33">
         <v>800000</v>
       </c>
       <c r="E79" s="12">
@@ -5794,10 +5793,10 @@
       <c r="B80" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C80" s="34">
+      <c r="C80" s="33">
         <v>940000</v>
       </c>
-      <c r="D80" s="34">
+      <c r="D80" s="33">
         <v>1350000</v>
       </c>
       <c r="E80" s="12">
@@ -5812,10 +5811,10 @@
       <c r="B81" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C81" s="34">
+      <c r="C81" s="33">
         <v>1490000</v>
       </c>
-      <c r="D81" s="34">
+      <c r="D81" s="33">
         <v>1200000</v>
       </c>
       <c r="E81" s="12">
@@ -5830,10 +5829,10 @@
       <c r="B82" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="34">
+      <c r="C82" s="33">
         <v>1410000</v>
       </c>
-      <c r="D82" s="34">
+      <c r="D82" s="33">
         <v>1400000</v>
       </c>
       <c r="E82" s="12">
@@ -5848,10 +5847,10 @@
       <c r="B83" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C83" s="34">
+      <c r="C83" s="33">
         <v>710000</v>
       </c>
-      <c r="D83" s="34">
+      <c r="D83" s="33">
         <v>1150000</v>
       </c>
       <c r="E83" s="12">
@@ -5866,10 +5865,10 @@
       <c r="B84" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C84" s="34">
+      <c r="C84" s="33">
         <v>1230000</v>
       </c>
-      <c r="D84" s="34">
+      <c r="D84" s="33">
         <v>950000</v>
       </c>
       <c r="E84" s="12">
@@ -5884,10 +5883,10 @@
       <c r="B85" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C85" s="34">
+      <c r="C85" s="33">
         <v>650000</v>
       </c>
-      <c r="D85" s="34">
+      <c r="D85" s="33">
         <v>850000</v>
       </c>
       <c r="E85" s="12">
@@ -5902,10 +5901,10 @@
       <c r="B86" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C86" s="34">
+      <c r="C86" s="33">
         <v>840000</v>
       </c>
-      <c r="D86" s="34">
+      <c r="D86" s="33">
         <v>1050000</v>
       </c>
       <c r="E86" s="12">
@@ -5920,10 +5919,10 @@
       <c r="B87" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C87" s="34">
+      <c r="C87" s="33">
         <v>640000</v>
       </c>
-      <c r="D87" s="34">
+      <c r="D87" s="33">
         <v>700000</v>
       </c>
       <c r="E87" s="12">
@@ -5938,10 +5937,10 @@
       <c r="B88" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C88" s="34">
+      <c r="C88" s="33">
         <v>740000</v>
       </c>
-      <c r="D88" s="34">
+      <c r="D88" s="33">
         <v>750000</v>
       </c>
       <c r="E88" s="12">
@@ -5956,10 +5955,10 @@
       <c r="B89" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C89" s="34">
+      <c r="C89" s="33">
         <v>1040000</v>
       </c>
-      <c r="D89" s="34">
+      <c r="D89" s="33">
         <v>800000</v>
       </c>
       <c r="E89" s="12">
@@ -5974,10 +5973,10 @@
       <c r="B90" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C90" s="34">
+      <c r="C90" s="33">
         <v>1040000</v>
       </c>
-      <c r="D90" s="34">
+      <c r="D90" s="33">
         <v>1400000</v>
       </c>
       <c r="E90" s="12">
@@ -5992,10 +5991,10 @@
       <c r="B91" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C91" s="34">
+      <c r="C91" s="33">
         <v>1280000</v>
       </c>
-      <c r="D91" s="34">
+      <c r="D91" s="33">
         <v>1050000</v>
       </c>
       <c r="E91" s="12">
@@ -6010,10 +6009,10 @@
       <c r="B92" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C92" s="34">
+      <c r="C92" s="33">
         <v>1540000</v>
       </c>
-      <c r="D92" s="34">
+      <c r="D92" s="33">
         <v>1150000</v>
       </c>
       <c r="E92" s="12">
@@ -6028,10 +6027,10 @@
       <c r="B93" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C93" s="34">
+      <c r="C93" s="33">
         <v>760000</v>
       </c>
-      <c r="D93" s="34">
+      <c r="D93" s="33">
         <v>700000</v>
       </c>
       <c r="E93" s="12">
@@ -6046,10 +6045,10 @@
       <c r="B94" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C94" s="34">
+      <c r="C94" s="33">
         <v>1510000</v>
       </c>
-      <c r="D94" s="34">
+      <c r="D94" s="33">
         <v>1400000</v>
       </c>
       <c r="E94" s="12">
@@ -6064,10 +6063,10 @@
       <c r="B95" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C95" s="34">
+      <c r="C95" s="33">
         <v>580000</v>
       </c>
-      <c r="D95" s="34">
+      <c r="D95" s="33">
         <v>900000</v>
       </c>
       <c r="E95" s="12">
@@ -6082,10 +6081,10 @@
       <c r="B96" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C96" s="34">
+      <c r="C96" s="33">
         <v>610000</v>
       </c>
-      <c r="D96" s="34">
+      <c r="D96" s="33">
         <v>800000</v>
       </c>
       <c r="E96" s="12">
@@ -6100,10 +6099,10 @@
       <c r="B97" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C97" s="34">
+      <c r="C97" s="33">
         <v>1030000</v>
       </c>
-      <c r="D97" s="34">
+      <c r="D97" s="33">
         <v>1250000</v>
       </c>
       <c r="E97" s="12">
@@ -6118,10 +6117,10 @@
       <c r="B98" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C98" s="34">
+      <c r="C98" s="33">
         <v>1030000</v>
       </c>
-      <c r="D98" s="34">
+      <c r="D98" s="33">
         <v>1100000</v>
       </c>
       <c r="E98" s="12">
@@ -6136,10 +6135,10 @@
       <c r="B99" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C99" s="34">
+      <c r="C99" s="33">
         <v>790000</v>
       </c>
-      <c r="D99" s="34">
+      <c r="D99" s="33">
         <v>750000</v>
       </c>
       <c r="E99" s="12">
@@ -6154,10 +6153,10 @@
       <c r="B100" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C100" s="34">
+      <c r="C100" s="33">
         <v>390000</v>
       </c>
-      <c r="D100" s="34">
+      <c r="D100" s="33">
         <v>700000</v>
       </c>
       <c r="E100" s="12">
@@ -6172,10 +6171,10 @@
       <c r="B101" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C101" s="34">
+      <c r="C101" s="33">
         <v>1600000</v>
       </c>
-      <c r="D101" s="34">
+      <c r="D101" s="33">
         <v>1200000</v>
       </c>
       <c r="E101" s="12">
@@ -6196,7 +6195,7 @@
   <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -6225,15 +6224,15 @@
       <c r="B2" s="16">
         <v>0.8</v>
       </c>
-      <c r="C2" s="23">
+      <c r="C2" s="22">
         <f>$B2*C$1</f>
         <v>2.4E-2</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="22">
         <f t="shared" ref="D2:E4" si="0">$B2*D$1</f>
         <v>4.0000000000000008E-2</v>
       </c>
-      <c r="E2" s="23">
+      <c r="E2" s="22">
         <f t="shared" si="0"/>
         <v>5.6000000000000008E-2</v>
       </c>
@@ -6245,15 +6244,15 @@
       <c r="B3" s="16">
         <v>1</v>
       </c>
-      <c r="C3" s="23">
+      <c r="C3" s="22">
         <f t="shared" ref="C3:C4" si="1">$B3*C$1</f>
         <v>0.03</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="22">
         <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="22">
         <f t="shared" si="0"/>
         <v>7.0000000000000007E-2</v>
       </c>
@@ -6265,15 +6264,15 @@
       <c r="B4" s="16">
         <v>1.2</v>
       </c>
-      <c r="C4" s="23">
+      <c r="C4" s="22">
         <f t="shared" si="1"/>
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="22">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="22">
         <f t="shared" si="0"/>
         <v>8.4000000000000005E-2</v>
       </c>
@@ -6292,9 +6291,9 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J6" s="9"/>
       <c r="K6" s="16"/>
-      <c r="L6" s="24"/>
+      <c r="L6" s="23"/>
       <c r="M6" s="21"/>
-      <c r="N6" s="24"/>
+      <c r="N6" s="23"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J7" s="9"/>
@@ -6306,9 +6305,9 @@
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J8" s="9"/>
       <c r="K8" s="16"/>
-      <c r="L8" s="24"/>
+      <c r="L8" s="23"/>
       <c r="M8" s="21"/>
-      <c r="N8" s="24"/>
+      <c r="N8" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6365,8 +6364,8 @@
         <v>1.1428571428571428</v>
       </c>
       <c r="F2" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" ref="F2:F33" si="0">IF(E2&lt;100%,"Below Target",IF(E2=100%,"Target Achieved","Above Target"))</f>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -6387,8 +6386,8 @@
         <v>1.1375</v>
       </c>
       <c r="F3" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="0"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -6409,8 +6408,8 @@
         <v>1.0266666666666666</v>
       </c>
       <c r="F4" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="0"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -6431,7 +6430,7 @@
         <v>0.72</v>
       </c>
       <c r="F5" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6453,7 +6452,7 @@
         <v>0.70909090909090911</v>
       </c>
       <c r="F6" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6475,7 +6474,7 @@
         <v>0.73</v>
       </c>
       <c r="F7" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6497,8 +6496,8 @@
         <v>1.2461538461538462</v>
       </c>
       <c r="F8" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="0"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6519,7 +6518,7 @@
         <v>0.88800000000000001</v>
       </c>
       <c r="F9" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6541,8 +6540,8 @@
         <v>1.3176470588235294</v>
       </c>
       <c r="F10" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="0"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6563,7 +6562,7 @@
         <v>0.85333333333333339</v>
       </c>
       <c r="F11" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6585,7 +6584,7 @@
         <v>0.76521739130434785</v>
       </c>
       <c r="F12" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6607,7 +6606,7 @@
         <v>0.6454545454545455</v>
       </c>
       <c r="F13" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6629,7 +6628,7 @@
         <v>0.98666666666666669</v>
       </c>
       <c r="F14" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6651,7 +6650,7 @@
         <v>0.70434782608695656</v>
       </c>
       <c r="F15" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6673,7 +6672,7 @@
         <v>0.73333333333333328</v>
       </c>
       <c r="F16" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6695,7 +6694,7 @@
         <v>0.73333333333333328</v>
       </c>
       <c r="F17" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6717,7 +6716,7 @@
         <v>0.91111111111111109</v>
       </c>
       <c r="F18" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6739,7 +6738,7 @@
         <v>0.85</v>
       </c>
       <c r="F19" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6761,8 +6760,8 @@
         <v>1.296</v>
       </c>
       <c r="F20" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="0"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -6783,8 +6782,8 @@
         <v>1.0608695652173914</v>
       </c>
       <c r="F21" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="0"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -6805,7 +6804,7 @@
         <v>0.92500000000000004</v>
       </c>
       <c r="F22" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6827,8 +6826,8 @@
         <v>1.0941176470588236</v>
       </c>
       <c r="F23" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="0"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -6849,8 +6848,8 @@
         <v>1.2117647058823529</v>
       </c>
       <c r="F24" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="0"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -6871,7 +6870,7 @@
         <v>0.76</v>
       </c>
       <c r="F25" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6893,8 +6892,8 @@
         <v>1.0705882352941176</v>
       </c>
       <c r="F26" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="0"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -6915,7 +6914,7 @@
         <v>0.76249999999999996</v>
       </c>
       <c r="F27" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6937,7 +6936,7 @@
         <v>0.76363636363636367</v>
       </c>
       <c r="F28" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -6959,8 +6958,8 @@
         <v>1.0142857142857142</v>
       </c>
       <c r="F29" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="0"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -6981,7 +6980,7 @@
         <v>0.96250000000000002</v>
       </c>
       <c r="F30" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7003,7 +7002,7 @@
         <v>0.63703703703703707</v>
       </c>
       <c r="F31" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7025,8 +7024,8 @@
         <v>1.0923076923076922</v>
       </c>
       <c r="F32" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="0"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -7047,7 +7046,7 @@
         <v>0.86</v>
       </c>
       <c r="F33" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7069,8 +7068,8 @@
         <v>1.3222222222222222</v>
       </c>
       <c r="F34" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" ref="F34:F65" si="1">IF(E34&lt;100%,"Below Target",IF(E34=100%,"Target Achieved","Above Target"))</f>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -7091,8 +7090,8 @@
         <v>1.125</v>
       </c>
       <c r="F35" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="1"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -7113,7 +7112,7 @@
         <v>0.7615384615384615</v>
       </c>
       <c r="F36" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7135,7 +7134,7 @@
         <v>0.78666666666666663</v>
       </c>
       <c r="F37" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7157,8 +7156,8 @@
         <v>1.3142857142857143</v>
       </c>
       <c r="F38" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="1"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -7179,8 +7178,8 @@
         <v>1.1636363636363636</v>
       </c>
       <c r="F39" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="1"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -7201,8 +7200,8 @@
         <v>1.0518518518518518</v>
       </c>
       <c r="F40" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="1"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -7223,7 +7222,7 @@
         <v>0.71304347826086956</v>
       </c>
       <c r="F41" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7245,8 +7244,8 @@
         <v>1.3090909090909091</v>
       </c>
       <c r="F42" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="1"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -7267,7 +7266,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F43" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7289,7 +7288,7 @@
         <v>0.6428571428571429</v>
       </c>
       <c r="F44" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7311,7 +7310,7 @@
         <v>0.6</v>
       </c>
       <c r="F45" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7333,8 +7332,8 @@
         <v>1.1333333333333333</v>
       </c>
       <c r="F46" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="1"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -7355,7 +7354,7 @@
         <v>0.97692307692307689</v>
       </c>
       <c r="F47" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7377,7 +7376,7 @@
         <v>0.93333333333333335</v>
       </c>
       <c r="F48" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7399,7 +7398,7 @@
         <v>0.96666666666666667</v>
       </c>
       <c r="F49" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7421,8 +7420,8 @@
         <v>1.2941176470588236</v>
       </c>
       <c r="F50" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="1"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -7443,7 +7442,7 @@
         <v>0.8</v>
       </c>
       <c r="F51" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7465,8 +7464,8 @@
         <v>1.2666666666666666</v>
       </c>
       <c r="F52" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="1"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -7487,7 +7486,7 @@
         <v>0.72941176470588232</v>
       </c>
       <c r="F53" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7509,7 +7508,7 @@
         <v>0.99130434782608701</v>
       </c>
       <c r="F54" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7531,7 +7530,7 @@
         <v>0.6</v>
       </c>
       <c r="F55" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7553,7 +7552,7 @@
         <v>0.6</v>
       </c>
       <c r="F56" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7575,7 +7574,7 @@
         <v>0.96</v>
       </c>
       <c r="F57" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7597,7 +7596,7 @@
         <v>0.97647058823529409</v>
       </c>
       <c r="F58" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7619,8 +7618,8 @@
         <v>1.1764705882352942</v>
       </c>
       <c r="F59" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="1"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -7641,7 +7640,7 @@
         <v>0.62352941176470589</v>
       </c>
       <c r="F60" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7663,7 +7662,7 @@
         <v>0.88421052631578945</v>
       </c>
       <c r="F61" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7685,8 +7684,8 @@
         <v>1.075</v>
       </c>
       <c r="F62" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="1"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -7707,7 +7706,7 @@
         <v>0.87142857142857144</v>
       </c>
       <c r="F63" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7729,7 +7728,7 @@
         <v>0.70588235294117652</v>
       </c>
       <c r="F64" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7751,7 +7750,7 @@
         <v>0.88749999999999996</v>
       </c>
       <c r="F65" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7773,8 +7772,8 @@
         <v>1.2470588235294118</v>
       </c>
       <c r="F66" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" ref="F66:F97" si="2">IF(E66&lt;100%,"Below Target",IF(E66=100%,"Target Achieved","Above Target"))</f>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -7795,8 +7794,8 @@
         <v>1.2384615384615385</v>
       </c>
       <c r="F67" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="2"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -7817,8 +7816,8 @@
         <v>1.0714285714285714</v>
       </c>
       <c r="F68" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="2"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -7839,8 +7838,8 @@
         <v>1.2933333333333332</v>
       </c>
       <c r="F69" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="2"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -7861,7 +7860,7 @@
         <v>0.875</v>
       </c>
       <c r="F70" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7883,7 +7882,7 @@
         <v>0.87407407407407411</v>
       </c>
       <c r="F71" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7905,7 +7904,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F72" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -7927,8 +7926,8 @@
         <v>1.1785714285714286</v>
       </c>
       <c r="F73" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="2"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -7949,8 +7948,8 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="F74" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="2"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -7971,8 +7970,8 @@
         <v>1.125</v>
       </c>
       <c r="F75" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="2"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -7993,7 +7992,7 @@
         <v>0.72222222222222221</v>
       </c>
       <c r="F76" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -8015,8 +8014,8 @@
         <v>1.1428571428571428</v>
       </c>
       <c r="F77" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="2"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -8037,7 +8036,7 @@
         <v>0.93043478260869561</v>
       </c>
       <c r="F78" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -8059,7 +8058,7 @@
         <v>0.6</v>
       </c>
       <c r="F79" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -8081,7 +8080,7 @@
         <v>0.6962962962962963</v>
       </c>
       <c r="F80" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -8103,8 +8102,8 @@
         <v>1.2416666666666667</v>
       </c>
       <c r="F81" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="2"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -8125,8 +8124,8 @@
         <v>1.0071428571428571</v>
       </c>
       <c r="F82" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="2"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -8147,7 +8146,7 @@
         <v>0.61739130434782608</v>
       </c>
       <c r="F83" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -8169,8 +8168,8 @@
         <v>1.2947368421052632</v>
       </c>
       <c r="F84" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="2"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -8191,7 +8190,7 @@
         <v>0.76470588235294112</v>
       </c>
       <c r="F85" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -8213,7 +8212,7 @@
         <v>0.8</v>
       </c>
       <c r="F86" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -8235,7 +8234,7 @@
         <v>0.91428571428571426</v>
       </c>
       <c r="F87" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -8257,7 +8256,7 @@
         <v>0.98666666666666669</v>
       </c>
       <c r="F88" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -8279,8 +8278,8 @@
         <v>1.3</v>
       </c>
       <c r="F89" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="2"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -8301,7 +8300,7 @@
         <v>0.74285714285714288</v>
       </c>
       <c r="F90" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -8323,8 +8322,8 @@
         <v>1.2190476190476192</v>
       </c>
       <c r="F91" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="2"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -8345,8 +8344,8 @@
         <v>1.3391304347826087</v>
       </c>
       <c r="F92" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="2"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -8367,8 +8366,8 @@
         <v>1.0857142857142856</v>
       </c>
       <c r="F93" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="2"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -8389,8 +8388,8 @@
         <v>1.0785714285714285</v>
       </c>
       <c r="F94" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="2"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -8411,7 +8410,7 @@
         <v>0.64444444444444449</v>
       </c>
       <c r="F95" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -8433,7 +8432,7 @@
         <v>0.76249999999999996</v>
       </c>
       <c r="F96" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -8455,7 +8454,7 @@
         <v>0.82399999999999995</v>
       </c>
       <c r="F97" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -8477,7 +8476,7 @@
         <v>0.9363636363636364</v>
       </c>
       <c r="F98" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" ref="F98:F101" si="3">IF(E98&lt;100%,"Below Target",IF(E98=100%,"Target Achieved","Above Target"))</f>
         <v>Below Target</v>
       </c>
     </row>
@@ -8499,8 +8498,8 @@
         <v>1.0533333333333332</v>
       </c>
       <c r="F99" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="3"/>
+        <v>Above Target</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -8521,7 +8520,7 @@
         <v>0.55714285714285716</v>
       </c>
       <c r="F100" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
+        <f t="shared" si="3"/>
         <v>Below Target</v>
       </c>
     </row>
@@ -8543,8 +8542,8 @@
         <v>1.3333333333333333</v>
       </c>
       <c r="F101" s="12" t="str">
-        <f>IF(Table3[[#This Row],[Target_Achievement]]&gt;100%,"Target Achieved","Below Target")</f>
-        <v>Target Achieved</v>
+        <f t="shared" si="3"/>
+        <v>Above Target</v>
       </c>
     </row>
   </sheetData>
@@ -8560,14 +8559,14 @@
   <dimension ref="A1:V101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" style="35" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" style="35" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" style="34" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" style="31" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -8582,10 +8581,10 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="32" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="14" t="s">
@@ -8597,7 +8596,7 @@
       <c r="G1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="29" t="s">
         <v>53</v>
       </c>
       <c r="K1" t="s">
@@ -8611,10 +8610,10 @@
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="34">
+      <c r="C2" s="33">
         <v>800000</v>
       </c>
-      <c r="D2" s="34">
+      <c r="D2" s="33">
         <v>700000</v>
       </c>
       <c r="E2" s="6">
@@ -8625,13 +8624,13 @@
         <f t="shared" ref="F2:F33" si="0">IF(E2&lt;100%,"Below Target",IF(E2=100%,"Target Achieved","Above Target"))</f>
         <v>Above Target</v>
       </c>
-      <c r="G2" s="29">
+      <c r="G2" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H2" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>40000</v>
+      <c r="H2" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>48000</v>
       </c>
       <c r="K2" s="20">
         <v>0.05</v>
@@ -8639,22 +8638,22 @@
       <c r="P2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="Q2" s="25" t="s">
+      <c r="Q2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="R2" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="25" t="s">
+      <c r="S2" s="24" t="s">
         <v>59</v>
       </c>
       <c r="T2" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="U2" s="25" t="s">
+      <c r="U2" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="V2" s="25" t="s">
+      <c r="V2" s="24" t="s">
         <v>53</v>
       </c>
     </row>
@@ -8665,10 +8664,10 @@
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="33">
         <v>910000</v>
       </c>
-      <c r="D3" s="34">
+      <c r="D3" s="33">
         <v>800000</v>
       </c>
       <c r="E3" s="6">
@@ -8679,33 +8678,33 @@
         <f t="shared" si="0"/>
         <v>Above Target</v>
       </c>
-      <c r="G3" s="29">
+      <c r="G3" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H3" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>45500</v>
+      <c r="H3" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>54600</v>
       </c>
       <c r="P3" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="Q3" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="R3" s="26" t="s">
+      <c r="R3" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="S3" s="27">
+      <c r="S3" s="26">
         <v>0.85</v>
       </c>
       <c r="T3" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="U3" s="26">
+      <c r="U3" s="25">
         <v>0.8</v>
       </c>
-      <c r="V3" s="26" t="s">
+      <c r="V3" s="25" t="s">
         <v>63</v>
       </c>
     </row>
@@ -8716,10 +8715,10 @@
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="33">
         <v>770000</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="33">
         <v>750000</v>
       </c>
       <c r="E4" s="6">
@@ -8730,33 +8729,33 @@
         <f t="shared" si="0"/>
         <v>Above Target</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H4" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>38500</v>
+      <c r="H4" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>46200</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="Q4" s="26" t="s">
+      <c r="Q4" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="26" t="s">
+      <c r="R4" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="S4" s="27">
+      <c r="S4" s="26">
         <v>1.25</v>
       </c>
       <c r="T4" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="U4" s="26">
+      <c r="U4" s="25">
         <v>1.2</v>
       </c>
-      <c r="V4" s="26" t="s">
+      <c r="V4" s="25" t="s">
         <v>65</v>
       </c>
     </row>
@@ -8767,10 +8766,10 @@
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="33">
         <v>540000</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="33">
         <v>750000</v>
       </c>
       <c r="E5" s="6">
@@ -8781,33 +8780,33 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H5" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>27000</v>
+      <c r="H5" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>21600</v>
       </c>
       <c r="P5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="Q5" s="26" t="s">
+      <c r="Q5" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="R5" s="26" t="s">
+      <c r="R5" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="S5" s="27">
+      <c r="S5" s="26">
         <v>0.95</v>
       </c>
       <c r="T5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="U5" s="26">
+      <c r="U5" s="25">
         <v>0.8</v>
       </c>
-      <c r="V5" s="26" t="s">
+      <c r="V5" s="25" t="s">
         <v>67</v>
       </c>
     </row>
@@ -8818,10 +8817,10 @@
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="33">
         <v>780000</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="33">
         <v>1100000</v>
       </c>
       <c r="E6" s="6">
@@ -8832,33 +8831,33 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H6" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>39000</v>
+      <c r="H6" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>31200</v>
       </c>
       <c r="P6" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="Q6" s="26" t="s">
+      <c r="Q6" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="R6" s="26" t="s">
+      <c r="R6" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="S6" s="28">
+      <c r="S6" s="27">
         <v>1.1667000000000001</v>
       </c>
       <c r="T6" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="U6" s="26">
+      <c r="U6" s="25">
         <v>1.2</v>
       </c>
-      <c r="V6" s="26" t="s">
+      <c r="V6" s="25" t="s">
         <v>70</v>
       </c>
     </row>
@@ -8869,10 +8868,10 @@
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="33">
         <v>730000</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="33">
         <v>1000000</v>
       </c>
       <c r="E7" s="6">
@@ -8883,13 +8882,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H7" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>36500</v>
+      <c r="H7" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>29200</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -8899,10 +8898,10 @@
       <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="33">
         <v>1620000</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="33">
         <v>1300000</v>
       </c>
       <c r="E8" s="6">
@@ -8913,13 +8912,13 @@
         <f t="shared" si="0"/>
         <v>Above Target</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H8" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>81000</v>
+      <c r="H8" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>97200</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -8929,10 +8928,10 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="33">
         <v>1110000</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="33">
         <v>1250000</v>
       </c>
       <c r="E9" s="6">
@@ -8943,13 +8942,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H9" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>55500</v>
+      <c r="H9" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>44400</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -8959,10 +8958,10 @@
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="33">
         <v>1120000</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>850000</v>
       </c>
       <c r="E10" s="6">
@@ -8973,13 +8972,13 @@
         <f t="shared" si="0"/>
         <v>Above Target</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H10" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>56000</v>
+      <c r="H10" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>67200</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -8989,10 +8988,10 @@
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="33">
         <v>640000</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="33">
         <v>750000</v>
       </c>
       <c r="E11" s="6">
@@ -9003,13 +9002,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H11" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>32000</v>
+      <c r="H11" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>25600</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -9019,10 +9018,10 @@
       <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="33">
         <v>880000</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="33">
         <v>1150000</v>
       </c>
       <c r="E12" s="6">
@@ -9033,13 +9032,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H12" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>44000</v>
+      <c r="H12" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>35200</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -9049,10 +9048,10 @@
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="33">
         <v>710000</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="33">
         <v>1100000</v>
       </c>
       <c r="E13" s="6">
@@ -9063,13 +9062,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H13" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>35500</v>
+      <c r="H13" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>28400</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -9079,10 +9078,10 @@
       <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="33">
         <v>740000</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="33">
         <v>750000</v>
       </c>
       <c r="E14" s="6">
@@ -9093,13 +9092,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H14" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>37000</v>
+      <c r="H14" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>29600</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -9109,10 +9108,10 @@
       <c r="B15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="33">
         <v>810000</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="33">
         <v>1150000</v>
       </c>
       <c r="E15" s="6">
@@ -9123,13 +9122,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H15" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>40500</v>
+      <c r="H15" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>32400</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -9139,10 +9138,10 @@
       <c r="B16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="33">
         <v>880000</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="33">
         <v>1200000</v>
       </c>
       <c r="E16" s="6">
@@ -9153,13 +9152,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H16" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>44000</v>
+      <c r="H16" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>35200</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -9169,10 +9168,10 @@
       <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="33">
         <v>990000</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="33">
         <v>1350000</v>
       </c>
       <c r="E17" s="6">
@@ -9183,13 +9182,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H17" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>49500</v>
+      <c r="H17" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>39600</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -9199,10 +9198,10 @@
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="33">
         <v>820000</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="33">
         <v>900000</v>
       </c>
       <c r="E18" s="6">
@@ -9213,13 +9212,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H18" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>41000</v>
+      <c r="H18" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>32800</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -9229,10 +9228,10 @@
       <c r="B19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="33">
         <v>680000</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="33">
         <v>800000</v>
       </c>
       <c r="E19" s="6">
@@ -9243,13 +9242,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G19" s="29">
+      <c r="G19" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H19" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>34000</v>
+      <c r="H19" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>27200</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -9259,10 +9258,10 @@
       <c r="B20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="33">
         <v>1620000</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="33">
         <v>1250000</v>
       </c>
       <c r="E20" s="6">
@@ -9273,13 +9272,13 @@
         <f t="shared" si="0"/>
         <v>Above Target</v>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H20" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>81000</v>
+      <c r="H20" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>97200</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -9289,10 +9288,10 @@
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="33">
         <v>1220000</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="33">
         <v>1150000</v>
       </c>
       <c r="E21" s="6">
@@ -9303,13 +9302,13 @@
         <f t="shared" si="0"/>
         <v>Above Target</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H21" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>61000</v>
+      <c r="H21" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>73200</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -9319,10 +9318,10 @@
       <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="33">
         <v>740000</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="33">
         <v>800000</v>
       </c>
       <c r="E22" s="6">
@@ -9333,13 +9332,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H22" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>37000</v>
+      <c r="H22" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>29600</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -9349,10 +9348,10 @@
       <c r="B23" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="33">
         <v>930000</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="33">
         <v>850000</v>
       </c>
       <c r="E23" s="6">
@@ -9363,13 +9362,13 @@
         <f t="shared" si="0"/>
         <v>Above Target</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H23" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>46500</v>
+      <c r="H23" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>55800</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -9379,10 +9378,10 @@
       <c r="B24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="33">
         <v>1030000</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="33">
         <v>850000</v>
       </c>
       <c r="E24" s="6">
@@ -9393,13 +9392,13 @@
         <f t="shared" si="0"/>
         <v>Above Target</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H24" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>51500</v>
+      <c r="H24" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>61800</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -9409,10 +9408,10 @@
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="33">
         <v>760000</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="33">
         <v>1000000</v>
       </c>
       <c r="E25" s="6">
@@ -9423,13 +9422,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H25" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>38000</v>
+      <c r="H25" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>30400</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -9439,10 +9438,10 @@
       <c r="B26" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="33">
         <v>910000</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="33">
         <v>850000</v>
       </c>
       <c r="E26" s="6">
@@ -9453,13 +9452,13 @@
         <f t="shared" si="0"/>
         <v>Above Target</v>
       </c>
-      <c r="G26" s="29">
+      <c r="G26" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H26" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>45500</v>
+      <c r="H26" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>54600</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -9469,10 +9468,10 @@
       <c r="B27" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="33">
         <v>610000</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="33">
         <v>800000</v>
       </c>
       <c r="E27" s="6">
@@ -9483,13 +9482,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G27" s="29">
+      <c r="G27" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H27" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>30500</v>
+      <c r="H27" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>24400</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -9499,10 +9498,10 @@
       <c r="B28" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="33">
         <v>840000</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="33">
         <v>1100000</v>
       </c>
       <c r="E28" s="6">
@@ -9513,13 +9512,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G28" s="29">
+      <c r="G28" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H28" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>42000</v>
+      <c r="H28" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>33600</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -9529,10 +9528,10 @@
       <c r="B29" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="33">
         <v>1420000</v>
       </c>
-      <c r="D29" s="34">
+      <c r="D29" s="33">
         <v>1400000</v>
       </c>
       <c r="E29" s="6">
@@ -9543,13 +9542,13 @@
         <f t="shared" si="0"/>
         <v>Above Target</v>
       </c>
-      <c r="G29" s="29">
+      <c r="G29" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H29" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>71000</v>
+      <c r="H29" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>85200</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -9559,10 +9558,10 @@
       <c r="B30" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="33">
         <v>770000</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="33">
         <v>800000</v>
       </c>
       <c r="E30" s="6">
@@ -9573,13 +9572,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H30" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>38500</v>
+      <c r="H30" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>30800</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -9589,10 +9588,10 @@
       <c r="B31" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="33">
         <v>860000</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="33">
         <v>1350000</v>
       </c>
       <c r="E31" s="6">
@@ -9603,13 +9602,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G31" s="29">
+      <c r="G31" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H31" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>43000</v>
+      <c r="H31" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>34400</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -9619,10 +9618,10 @@
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="34">
+      <c r="C32" s="33">
         <v>1420000</v>
       </c>
-      <c r="D32" s="34">
+      <c r="D32" s="33">
         <v>1300000</v>
       </c>
       <c r="E32" s="6">
@@ -9633,13 +9632,13 @@
         <f t="shared" si="0"/>
         <v>Above Target</v>
       </c>
-      <c r="G32" s="29">
+      <c r="G32" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H32" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>71000</v>
+      <c r="H32" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>85200</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -9649,10 +9648,10 @@
       <c r="B33" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="33">
         <v>860000</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="33">
         <v>1000000</v>
       </c>
       <c r="E33" s="6">
@@ -9663,13 +9662,13 @@
         <f t="shared" si="0"/>
         <v>Below Target</v>
       </c>
-      <c r="G33" s="29">
+      <c r="G33" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H33" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>43000</v>
+      <c r="H33" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>34400</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -9679,10 +9678,10 @@
       <c r="B34" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="33">
         <v>1190000</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="33">
         <v>900000</v>
       </c>
       <c r="E34" s="6">
@@ -9693,13 +9692,13 @@
         <f t="shared" ref="F34:F65" si="1">IF(E34&lt;100%,"Below Target",IF(E34=100%,"Target Achieved","Above Target"))</f>
         <v>Above Target</v>
       </c>
-      <c r="G34" s="29">
+      <c r="G34" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H34" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>59500</v>
+      <c r="H34" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>71400</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -9709,10 +9708,10 @@
       <c r="B35" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="33">
         <v>1350000</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="33">
         <v>1200000</v>
       </c>
       <c r="E35" s="6">
@@ -9723,13 +9722,13 @@
         <f t="shared" si="1"/>
         <v>Above Target</v>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H35" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>67500</v>
+      <c r="H35" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>81000</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -9739,10 +9738,10 @@
       <c r="B36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="33">
         <v>990000</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="33">
         <v>1300000</v>
       </c>
       <c r="E36" s="6">
@@ -9753,13 +9752,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G36" s="29">
+      <c r="G36" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H36" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>49500</v>
+      <c r="H36" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>39600</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -9769,10 +9768,10 @@
       <c r="B37" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="34">
+      <c r="C37" s="33">
         <v>590000</v>
       </c>
-      <c r="D37" s="34">
+      <c r="D37" s="33">
         <v>750000</v>
       </c>
       <c r="E37" s="6">
@@ -9783,13 +9782,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G37" s="29">
+      <c r="G37" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H37" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>29500</v>
+      <c r="H37" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>23600</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -9799,10 +9798,10 @@
       <c r="B38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="33">
         <v>920000</v>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="33">
         <v>700000</v>
       </c>
       <c r="E38" s="6">
@@ -9813,13 +9812,13 @@
         <f t="shared" si="1"/>
         <v>Above Target</v>
       </c>
-      <c r="G38" s="29">
+      <c r="G38" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H38" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>46000</v>
+      <c r="H38" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>55200</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -9829,10 +9828,10 @@
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="34">
+      <c r="C39" s="33">
         <v>1280000</v>
       </c>
-      <c r="D39" s="34">
+      <c r="D39" s="33">
         <v>1100000</v>
       </c>
       <c r="E39" s="6">
@@ -9843,13 +9842,13 @@
         <f t="shared" si="1"/>
         <v>Above Target</v>
       </c>
-      <c r="G39" s="29">
+      <c r="G39" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H39" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>64000</v>
+      <c r="H39" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>76800</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -9859,10 +9858,10 @@
       <c r="B40" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="34">
+      <c r="C40" s="33">
         <v>1420000</v>
       </c>
-      <c r="D40" s="34">
+      <c r="D40" s="33">
         <v>1350000</v>
       </c>
       <c r="E40" s="6">
@@ -9873,13 +9872,13 @@
         <f t="shared" si="1"/>
         <v>Above Target</v>
       </c>
-      <c r="G40" s="29">
+      <c r="G40" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H40" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>71000</v>
+      <c r="H40" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>85200</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -9889,10 +9888,10 @@
       <c r="B41" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="34">
+      <c r="C41" s="33">
         <v>820000</v>
       </c>
-      <c r="D41" s="34">
+      <c r="D41" s="33">
         <v>1150000</v>
       </c>
       <c r="E41" s="6">
@@ -9903,13 +9902,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G41" s="29">
+      <c r="G41" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H41" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>41000</v>
+      <c r="H41" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>32800</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -9919,10 +9918,10 @@
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="34">
+      <c r="C42" s="33">
         <v>1440000</v>
       </c>
-      <c r="D42" s="34">
+      <c r="D42" s="33">
         <v>1100000</v>
       </c>
       <c r="E42" s="6">
@@ -9933,13 +9932,13 @@
         <f t="shared" si="1"/>
         <v>Above Target</v>
       </c>
-      <c r="G42" s="29">
+      <c r="G42" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H42" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>72000</v>
+      <c r="H42" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>86400</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -9949,10 +9948,10 @@
       <c r="B43" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="33">
         <v>770000</v>
       </c>
-      <c r="D43" s="34">
+      <c r="D43" s="33">
         <v>1400000</v>
       </c>
       <c r="E43" s="6">
@@ -9963,13 +9962,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G43" s="29">
+      <c r="G43" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H43" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>38500</v>
+      <c r="H43" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>30800</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -9979,10 +9978,10 @@
       <c r="B44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="34">
+      <c r="C44" s="33">
         <v>450000</v>
       </c>
-      <c r="D44" s="34">
+      <c r="D44" s="33">
         <v>700000</v>
       </c>
       <c r="E44" s="6">
@@ -9993,13 +9992,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G44" s="29">
+      <c r="G44" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H44" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>22500</v>
+      <c r="H44" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>18000</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -10009,10 +10008,10 @@
       <c r="B45" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="34">
+      <c r="C45" s="33">
         <v>510000</v>
       </c>
-      <c r="D45" s="34">
+      <c r="D45" s="33">
         <v>850000</v>
       </c>
       <c r="E45" s="6">
@@ -10023,13 +10022,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G45" s="29">
+      <c r="G45" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H45" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>25500</v>
+      <c r="H45" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>20400</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -10039,10 +10038,10 @@
       <c r="B46" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C46" s="34">
+      <c r="C46" s="33">
         <v>850000</v>
       </c>
-      <c r="D46" s="34">
+      <c r="D46" s="33">
         <v>750000</v>
       </c>
       <c r="E46" s="6">
@@ -10053,13 +10052,13 @@
         <f t="shared" si="1"/>
         <v>Above Target</v>
       </c>
-      <c r="G46" s="29">
+      <c r="G46" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H46" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>42500</v>
+      <c r="H46" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>51000</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -10069,10 +10068,10 @@
       <c r="B47" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C47" s="34">
+      <c r="C47" s="33">
         <v>1270000</v>
       </c>
-      <c r="D47" s="34">
+      <c r="D47" s="33">
         <v>1300000</v>
       </c>
       <c r="E47" s="6">
@@ -10083,13 +10082,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G47" s="29">
+      <c r="G47" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H47" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>63500</v>
+      <c r="H47" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>50800</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -10099,10 +10098,10 @@
       <c r="B48" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="34">
+      <c r="C48" s="33">
         <v>1120000</v>
       </c>
-      <c r="D48" s="34">
+      <c r="D48" s="33">
         <v>1200000</v>
       </c>
       <c r="E48" s="6">
@@ -10113,13 +10112,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G48" s="29">
+      <c r="G48" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H48" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>56000</v>
+      <c r="H48" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>44800</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -10129,10 +10128,10 @@
       <c r="B49" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="34">
+      <c r="C49" s="33">
         <v>870000</v>
       </c>
-      <c r="D49" s="34">
+      <c r="D49" s="33">
         <v>900000</v>
       </c>
       <c r="E49" s="6">
@@ -10143,13 +10142,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G49" s="29">
+      <c r="G49" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H49" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>43500</v>
+      <c r="H49" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>34800</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -10159,10 +10158,10 @@
       <c r="B50" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C50" s="34">
+      <c r="C50" s="33">
         <v>1100000</v>
       </c>
-      <c r="D50" s="34">
+      <c r="D50" s="33">
         <v>850000</v>
       </c>
       <c r="E50" s="6">
@@ -10173,13 +10172,13 @@
         <f t="shared" si="1"/>
         <v>Above Target</v>
       </c>
-      <c r="G50" s="29">
+      <c r="G50" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H50" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>55000</v>
+      <c r="H50" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>66000</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -10189,10 +10188,10 @@
       <c r="B51" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C51" s="34">
+      <c r="C51" s="33">
         <v>1000000</v>
       </c>
-      <c r="D51" s="34">
+      <c r="D51" s="33">
         <v>1250000</v>
       </c>
       <c r="E51" s="6">
@@ -10203,13 +10202,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G51" s="29">
+      <c r="G51" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H51" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>50000</v>
+      <c r="H51" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>40000</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -10219,10 +10218,10 @@
       <c r="B52" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C52" s="34">
+      <c r="C52" s="33">
         <v>1330000</v>
       </c>
-      <c r="D52" s="34">
+      <c r="D52" s="33">
         <v>1050000</v>
       </c>
       <c r="E52" s="6">
@@ -10233,13 +10232,13 @@
         <f t="shared" si="1"/>
         <v>Above Target</v>
       </c>
-      <c r="G52" s="29">
+      <c r="G52" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H52" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>66500</v>
+      <c r="H52" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>79800</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -10249,10 +10248,10 @@
       <c r="B53" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C53" s="34">
+      <c r="C53" s="33">
         <v>620000</v>
       </c>
-      <c r="D53" s="34">
+      <c r="D53" s="33">
         <v>850000</v>
       </c>
       <c r="E53" s="6">
@@ -10263,13 +10262,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G53" s="29">
+      <c r="G53" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H53" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>31000</v>
+      <c r="H53" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>24800</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -10279,10 +10278,10 @@
       <c r="B54" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C54" s="34">
+      <c r="C54" s="33">
         <v>1140000</v>
       </c>
-      <c r="D54" s="34">
+      <c r="D54" s="33">
         <v>1150000</v>
       </c>
       <c r="E54" s="6">
@@ -10293,13 +10292,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G54" s="29">
+      <c r="G54" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H54" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>57000</v>
+      <c r="H54" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>45600</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -10309,10 +10308,10 @@
       <c r="B55" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C55" s="34">
+      <c r="C55" s="33">
         <v>420000</v>
       </c>
-      <c r="D55" s="34">
+      <c r="D55" s="33">
         <v>700000</v>
       </c>
       <c r="E55" s="6">
@@ -10323,13 +10322,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G55" s="29">
+      <c r="G55" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H55" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>21000</v>
+      <c r="H55" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>16800</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -10339,10 +10338,10 @@
       <c r="B56" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C56" s="34">
+      <c r="C56" s="33">
         <v>510000</v>
       </c>
-      <c r="D56" s="34">
+      <c r="D56" s="33">
         <v>850000</v>
       </c>
       <c r="E56" s="6">
@@ -10353,13 +10352,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G56" s="29">
+      <c r="G56" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H56" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>25500</v>
+      <c r="H56" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>20400</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -10369,10 +10368,10 @@
       <c r="B57" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C57" s="34">
+      <c r="C57" s="33">
         <v>720000</v>
       </c>
-      <c r="D57" s="34">
+      <c r="D57" s="33">
         <v>750000</v>
       </c>
       <c r="E57" s="6">
@@ -10383,13 +10382,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G57" s="29">
+      <c r="G57" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H57" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>36000</v>
+      <c r="H57" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>28800</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -10399,10 +10398,10 @@
       <c r="B58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C58" s="34">
+      <c r="C58" s="33">
         <v>830000</v>
       </c>
-      <c r="D58" s="34">
+      <c r="D58" s="33">
         <v>850000</v>
       </c>
       <c r="E58" s="6">
@@ -10413,13 +10412,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G58" s="29">
+      <c r="G58" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H58" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>41500</v>
+      <c r="H58" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>33200</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -10429,10 +10428,10 @@
       <c r="B59" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C59" s="34">
+      <c r="C59" s="33">
         <v>1000000</v>
       </c>
-      <c r="D59" s="34">
+      <c r="D59" s="33">
         <v>850000</v>
       </c>
       <c r="E59" s="6">
@@ -10443,13 +10442,13 @@
         <f t="shared" si="1"/>
         <v>Above Target</v>
       </c>
-      <c r="G59" s="29">
+      <c r="G59" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H59" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>50000</v>
+      <c r="H59" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>60000</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -10459,10 +10458,10 @@
       <c r="B60" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C60" s="34">
+      <c r="C60" s="33">
         <v>530000</v>
       </c>
-      <c r="D60" s="34">
+      <c r="D60" s="33">
         <v>850000</v>
       </c>
       <c r="E60" s="6">
@@ -10473,13 +10472,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G60" s="29">
+      <c r="G60" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H60" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>26500</v>
+      <c r="H60" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>21200</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -10489,10 +10488,10 @@
       <c r="B61" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C61" s="34">
+      <c r="C61" s="33">
         <v>840000</v>
       </c>
-      <c r="D61" s="34">
+      <c r="D61" s="33">
         <v>950000</v>
       </c>
       <c r="E61" s="6">
@@ -10503,13 +10502,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G61" s="29">
+      <c r="G61" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H61" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>42000</v>
+      <c r="H61" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>33600</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -10519,10 +10518,10 @@
       <c r="B62" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C62" s="34">
+      <c r="C62" s="33">
         <v>1290000</v>
       </c>
-      <c r="D62" s="34">
+      <c r="D62" s="33">
         <v>1200000</v>
       </c>
       <c r="E62" s="6">
@@ -10533,13 +10532,13 @@
         <f t="shared" si="1"/>
         <v>Above Target</v>
       </c>
-      <c r="G62" s="29">
+      <c r="G62" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H62" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>64500</v>
+      <c r="H62" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>77400</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -10549,10 +10548,10 @@
       <c r="B63" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C63" s="34">
+      <c r="C63" s="33">
         <v>610000</v>
       </c>
-      <c r="D63" s="34">
+      <c r="D63" s="33">
         <v>700000</v>
       </c>
       <c r="E63" s="6">
@@ -10563,13 +10562,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G63" s="29">
+      <c r="G63" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H63" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>30500</v>
+      <c r="H63" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>24400</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -10579,10 +10578,10 @@
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="34">
+      <c r="C64" s="33">
         <v>600000</v>
       </c>
-      <c r="D64" s="34">
+      <c r="D64" s="33">
         <v>850000</v>
       </c>
       <c r="E64" s="6">
@@ -10593,13 +10592,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G64" s="29">
+      <c r="G64" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H64" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>30000</v>
+      <c r="H64" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>24000</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -10609,10 +10608,10 @@
       <c r="B65" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C65" s="34">
+      <c r="C65" s="33">
         <v>710000</v>
       </c>
-      <c r="D65" s="34">
+      <c r="D65" s="33">
         <v>800000</v>
       </c>
       <c r="E65" s="6">
@@ -10623,13 +10622,13 @@
         <f t="shared" si="1"/>
         <v>Below Target</v>
       </c>
-      <c r="G65" s="29">
+      <c r="G65" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H65" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>35500</v>
+      <c r="H65" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>28400</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -10639,10 +10638,10 @@
       <c r="B66" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="34">
+      <c r="C66" s="33">
         <v>1060000</v>
       </c>
-      <c r="D66" s="34">
+      <c r="D66" s="33">
         <v>850000</v>
       </c>
       <c r="E66" s="6">
@@ -10653,13 +10652,13 @@
         <f t="shared" ref="F66:F97" si="2">IF(E66&lt;100%,"Below Target",IF(E66=100%,"Target Achieved","Above Target"))</f>
         <v>Above Target</v>
       </c>
-      <c r="G66" s="29">
+      <c r="G66" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H66" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>53000</v>
+      <c r="H66" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>63600</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -10669,10 +10668,10 @@
       <c r="B67" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C67" s="34">
+      <c r="C67" s="33">
         <v>1610000</v>
       </c>
-      <c r="D67" s="34">
+      <c r="D67" s="33">
         <v>1300000</v>
       </c>
       <c r="E67" s="6">
@@ -10683,13 +10682,13 @@
         <f t="shared" si="2"/>
         <v>Above Target</v>
       </c>
-      <c r="G67" s="29">
+      <c r="G67" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H67" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>80500</v>
+      <c r="H67" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>96600</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -10699,10 +10698,10 @@
       <c r="B68" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C68" s="34">
+      <c r="C68" s="33">
         <v>750000</v>
       </c>
-      <c r="D68" s="34">
+      <c r="D68" s="33">
         <v>700000</v>
       </c>
       <c r="E68" s="6">
@@ -10713,13 +10712,13 @@
         <f t="shared" si="2"/>
         <v>Above Target</v>
       </c>
-      <c r="G68" s="29">
+      <c r="G68" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H68" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>37500</v>
+      <c r="H68" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>45000</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -10729,10 +10728,10 @@
       <c r="B69" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C69" s="34">
+      <c r="C69" s="33">
         <v>970000</v>
       </c>
-      <c r="D69" s="34">
+      <c r="D69" s="33">
         <v>750000</v>
       </c>
       <c r="E69" s="6">
@@ -10743,13 +10742,13 @@
         <f t="shared" si="2"/>
         <v>Above Target</v>
       </c>
-      <c r="G69" s="29">
+      <c r="G69" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H69" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>48500</v>
+      <c r="H69" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>58200</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -10759,10 +10758,10 @@
       <c r="B70" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C70" s="34">
+      <c r="C70" s="33">
         <v>700000</v>
       </c>
-      <c r="D70" s="34">
+      <c r="D70" s="33">
         <v>800000</v>
       </c>
       <c r="E70" s="6">
@@ -10773,13 +10772,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G70" s="29">
+      <c r="G70" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H70" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>35000</v>
+      <c r="H70" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>28000</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -10789,10 +10788,10 @@
       <c r="B71" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C71" s="34">
+      <c r="C71" s="33">
         <v>1180000</v>
       </c>
-      <c r="D71" s="34">
+      <c r="D71" s="33">
         <v>1350000</v>
       </c>
       <c r="E71" s="6">
@@ -10803,13 +10802,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G71" s="29">
+      <c r="G71" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H71" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>59000</v>
+      <c r="H71" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>47200</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -10819,10 +10818,10 @@
       <c r="B72" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C72" s="34">
+      <c r="C72" s="33">
         <v>550000</v>
       </c>
-      <c r="D72" s="34">
+      <c r="D72" s="33">
         <v>1000000</v>
       </c>
       <c r="E72" s="6">
@@ -10833,13 +10832,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G72" s="29">
+      <c r="G72" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H72" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>27500</v>
+      <c r="H72" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>22000</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -10849,10 +10848,10 @@
       <c r="B73" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C73" s="34">
+      <c r="C73" s="33">
         <v>1650000</v>
       </c>
-      <c r="D73" s="34">
+      <c r="D73" s="33">
         <v>1400000</v>
       </c>
       <c r="E73" s="6">
@@ -10863,13 +10862,13 @@
         <f t="shared" si="2"/>
         <v>Above Target</v>
       </c>
-      <c r="G73" s="29">
+      <c r="G73" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H73" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>82500</v>
+      <c r="H73" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>99000</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -10879,10 +10878,10 @@
       <c r="B74" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C74" s="34">
+      <c r="C74" s="33">
         <v>1110000</v>
       </c>
-      <c r="D74" s="34">
+      <c r="D74" s="33">
         <v>1000000</v>
       </c>
       <c r="E74" s="6">
@@ -10893,13 +10892,13 @@
         <f t="shared" si="2"/>
         <v>Above Target</v>
       </c>
-      <c r="G74" s="29">
+      <c r="G74" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H74" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>55500</v>
+      <c r="H74" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>66600</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -10909,10 +10908,10 @@
       <c r="B75" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C75" s="34">
+      <c r="C75" s="33">
         <v>1350000</v>
       </c>
-      <c r="D75" s="34">
+      <c r="D75" s="33">
         <v>1200000</v>
       </c>
       <c r="E75" s="6">
@@ -10923,13 +10922,13 @@
         <f t="shared" si="2"/>
         <v>Above Target</v>
       </c>
-      <c r="G75" s="29">
+      <c r="G75" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H75" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>67500</v>
+      <c r="H75" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>81000</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -10939,10 +10938,10 @@
       <c r="B76" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C76" s="34">
+      <c r="C76" s="33">
         <v>650000</v>
       </c>
-      <c r="D76" s="34">
+      <c r="D76" s="33">
         <v>900000</v>
       </c>
       <c r="E76" s="6">
@@ -10953,13 +10952,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G76" s="29">
+      <c r="G76" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H76" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>32500</v>
+      <c r="H76" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>26000</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -10969,10 +10968,10 @@
       <c r="B77" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C77" s="34">
+      <c r="C77" s="33">
         <v>800000</v>
       </c>
-      <c r="D77" s="34">
+      <c r="D77" s="33">
         <v>700000</v>
       </c>
       <c r="E77" s="6">
@@ -10983,13 +10982,13 @@
         <f t="shared" si="2"/>
         <v>Above Target</v>
       </c>
-      <c r="G77" s="29">
+      <c r="G77" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H77" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>40000</v>
+      <c r="H77" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>48000</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -10999,10 +10998,10 @@
       <c r="B78" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C78" s="34">
+      <c r="C78" s="33">
         <v>1070000</v>
       </c>
-      <c r="D78" s="34">
+      <c r="D78" s="33">
         <v>1150000</v>
       </c>
       <c r="E78" s="6">
@@ -11013,13 +11012,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G78" s="29">
+      <c r="G78" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H78" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>53500</v>
+      <c r="H78" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>42800</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -11029,10 +11028,10 @@
       <c r="B79" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C79" s="34">
+      <c r="C79" s="33">
         <v>480000</v>
       </c>
-      <c r="D79" s="34">
+      <c r="D79" s="33">
         <v>800000</v>
       </c>
       <c r="E79" s="6">
@@ -11043,13 +11042,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G79" s="29">
+      <c r="G79" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H79" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>24000</v>
+      <c r="H79" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>19200</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -11059,10 +11058,10 @@
       <c r="B80" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C80" s="34">
+      <c r="C80" s="33">
         <v>940000</v>
       </c>
-      <c r="D80" s="34">
+      <c r="D80" s="33">
         <v>1350000</v>
       </c>
       <c r="E80" s="6">
@@ -11073,13 +11072,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G80" s="29">
+      <c r="G80" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H80" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>47000</v>
+      <c r="H80" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>37600</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -11089,10 +11088,10 @@
       <c r="B81" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C81" s="34">
+      <c r="C81" s="33">
         <v>1490000</v>
       </c>
-      <c r="D81" s="34">
+      <c r="D81" s="33">
         <v>1200000</v>
       </c>
       <c r="E81" s="6">
@@ -11103,13 +11102,13 @@
         <f t="shared" si="2"/>
         <v>Above Target</v>
       </c>
-      <c r="G81" s="29">
+      <c r="G81" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H81" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>74500</v>
+      <c r="H81" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>89400</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -11119,10 +11118,10 @@
       <c r="B82" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="34">
+      <c r="C82" s="33">
         <v>1410000</v>
       </c>
-      <c r="D82" s="34">
+      <c r="D82" s="33">
         <v>1400000</v>
       </c>
       <c r="E82" s="6">
@@ -11133,13 +11132,13 @@
         <f t="shared" si="2"/>
         <v>Above Target</v>
       </c>
-      <c r="G82" s="29">
+      <c r="G82" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H82" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>70500</v>
+      <c r="H82" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>84600</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -11149,10 +11148,10 @@
       <c r="B83" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C83" s="34">
+      <c r="C83" s="33">
         <v>710000</v>
       </c>
-      <c r="D83" s="34">
+      <c r="D83" s="33">
         <v>1150000</v>
       </c>
       <c r="E83" s="6">
@@ -11163,13 +11162,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G83" s="29">
+      <c r="G83" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H83" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>35500</v>
+      <c r="H83" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>28400</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -11179,10 +11178,10 @@
       <c r="B84" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C84" s="34">
+      <c r="C84" s="33">
         <v>1230000</v>
       </c>
-      <c r="D84" s="34">
+      <c r="D84" s="33">
         <v>950000</v>
       </c>
       <c r="E84" s="6">
@@ -11193,13 +11192,13 @@
         <f t="shared" si="2"/>
         <v>Above Target</v>
       </c>
-      <c r="G84" s="29">
+      <c r="G84" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H84" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>61500</v>
+      <c r="H84" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>73800</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -11209,10 +11208,10 @@
       <c r="B85" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C85" s="34">
+      <c r="C85" s="33">
         <v>650000</v>
       </c>
-      <c r="D85" s="34">
+      <c r="D85" s="33">
         <v>850000</v>
       </c>
       <c r="E85" s="6">
@@ -11223,13 +11222,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G85" s="29">
+      <c r="G85" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H85" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>32500</v>
+      <c r="H85" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>26000</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -11239,10 +11238,10 @@
       <c r="B86" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C86" s="34">
+      <c r="C86" s="33">
         <v>840000</v>
       </c>
-      <c r="D86" s="34">
+      <c r="D86" s="33">
         <v>1050000</v>
       </c>
       <c r="E86" s="6">
@@ -11253,13 +11252,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G86" s="29">
+      <c r="G86" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H86" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>42000</v>
+      <c r="H86" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>33600</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -11269,10 +11268,10 @@
       <c r="B87" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C87" s="34">
+      <c r="C87" s="33">
         <v>640000</v>
       </c>
-      <c r="D87" s="34">
+      <c r="D87" s="33">
         <v>700000</v>
       </c>
       <c r="E87" s="6">
@@ -11283,13 +11282,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G87" s="29">
+      <c r="G87" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H87" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>32000</v>
+      <c r="H87" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>25600</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -11299,10 +11298,10 @@
       <c r="B88" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C88" s="34">
+      <c r="C88" s="33">
         <v>740000</v>
       </c>
-      <c r="D88" s="34">
+      <c r="D88" s="33">
         <v>750000</v>
       </c>
       <c r="E88" s="6">
@@ -11313,13 +11312,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G88" s="29">
+      <c r="G88" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H88" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>37000</v>
+      <c r="H88" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>29600</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -11329,10 +11328,10 @@
       <c r="B89" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C89" s="34">
+      <c r="C89" s="33">
         <v>1040000</v>
       </c>
-      <c r="D89" s="34">
+      <c r="D89" s="33">
         <v>800000</v>
       </c>
       <c r="E89" s="6">
@@ -11343,13 +11342,13 @@
         <f t="shared" si="2"/>
         <v>Above Target</v>
       </c>
-      <c r="G89" s="29">
+      <c r="G89" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H89" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>52000</v>
+      <c r="H89" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>62400</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -11359,10 +11358,10 @@
       <c r="B90" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C90" s="34">
+      <c r="C90" s="33">
         <v>1040000</v>
       </c>
-      <c r="D90" s="34">
+      <c r="D90" s="33">
         <v>1400000</v>
       </c>
       <c r="E90" s="6">
@@ -11373,13 +11372,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G90" s="29">
+      <c r="G90" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H90" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>52000</v>
+      <c r="H90" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>41600</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -11389,10 +11388,10 @@
       <c r="B91" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C91" s="34">
+      <c r="C91" s="33">
         <v>1280000</v>
       </c>
-      <c r="D91" s="34">
+      <c r="D91" s="33">
         <v>1050000</v>
       </c>
       <c r="E91" s="6">
@@ -11403,13 +11402,13 @@
         <f t="shared" si="2"/>
         <v>Above Target</v>
       </c>
-      <c r="G91" s="29">
+      <c r="G91" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H91" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>64000</v>
+      <c r="H91" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>76800</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -11419,10 +11418,10 @@
       <c r="B92" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C92" s="34">
+      <c r="C92" s="33">
         <v>1540000</v>
       </c>
-      <c r="D92" s="34">
+      <c r="D92" s="33">
         <v>1150000</v>
       </c>
       <c r="E92" s="6">
@@ -11433,13 +11432,13 @@
         <f t="shared" si="2"/>
         <v>Above Target</v>
       </c>
-      <c r="G92" s="29">
+      <c r="G92" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H92" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>77000</v>
+      <c r="H92" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>92400</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -11449,10 +11448,10 @@
       <c r="B93" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C93" s="34">
+      <c r="C93" s="33">
         <v>760000</v>
       </c>
-      <c r="D93" s="34">
+      <c r="D93" s="33">
         <v>700000</v>
       </c>
       <c r="E93" s="6">
@@ -11463,13 +11462,13 @@
         <f t="shared" si="2"/>
         <v>Above Target</v>
       </c>
-      <c r="G93" s="29">
+      <c r="G93" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H93" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>38000</v>
+      <c r="H93" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>45600</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -11479,10 +11478,10 @@
       <c r="B94" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C94" s="34">
+      <c r="C94" s="33">
         <v>1510000</v>
       </c>
-      <c r="D94" s="34">
+      <c r="D94" s="33">
         <v>1400000</v>
       </c>
       <c r="E94" s="6">
@@ -11493,13 +11492,13 @@
         <f t="shared" si="2"/>
         <v>Above Target</v>
       </c>
-      <c r="G94" s="29">
+      <c r="G94" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H94" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>75500</v>
+      <c r="H94" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>90600</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -11509,10 +11508,10 @@
       <c r="B95" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C95" s="34">
+      <c r="C95" s="33">
         <v>580000</v>
       </c>
-      <c r="D95" s="34">
+      <c r="D95" s="33">
         <v>900000</v>
       </c>
       <c r="E95" s="6">
@@ -11523,13 +11522,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G95" s="29">
+      <c r="G95" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H95" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>29000</v>
+      <c r="H95" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>23200</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -11539,10 +11538,10 @@
       <c r="B96" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C96" s="34">
+      <c r="C96" s="33">
         <v>610000</v>
       </c>
-      <c r="D96" s="34">
+      <c r="D96" s="33">
         <v>800000</v>
       </c>
       <c r="E96" s="6">
@@ -11553,13 +11552,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G96" s="29">
+      <c r="G96" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H96" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>30500</v>
+      <c r="H96" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>24400</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -11569,10 +11568,10 @@
       <c r="B97" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C97" s="34">
+      <c r="C97" s="33">
         <v>1030000</v>
       </c>
-      <c r="D97" s="34">
+      <c r="D97" s="33">
         <v>1250000</v>
       </c>
       <c r="E97" s="6">
@@ -11583,13 +11582,13 @@
         <f t="shared" si="2"/>
         <v>Below Target</v>
       </c>
-      <c r="G97" s="29">
+      <c r="G97" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H97" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>51500</v>
+      <c r="H97" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>41200</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -11599,10 +11598,10 @@
       <c r="B98" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C98" s="34">
+      <c r="C98" s="33">
         <v>1030000</v>
       </c>
-      <c r="D98" s="34">
+      <c r="D98" s="33">
         <v>1100000</v>
       </c>
       <c r="E98" s="6">
@@ -11610,16 +11609,16 @@
         <v>0.9363636363636364</v>
       </c>
       <c r="F98" s="6" t="str">
-        <f t="shared" ref="F98:F129" si="3">IF(E98&lt;100%,"Below Target",IF(E98=100%,"Target Achieved","Above Target"))</f>
+        <f t="shared" ref="F98:F101" si="3">IF(E98&lt;100%,"Below Target",IF(E98=100%,"Target Achieved","Above Target"))</f>
         <v>Below Target</v>
       </c>
-      <c r="G98" s="29">
+      <c r="G98" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H98" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>51500</v>
+      <c r="H98" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>41200</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -11629,10 +11628,10 @@
       <c r="B99" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C99" s="34">
+      <c r="C99" s="33">
         <v>790000</v>
       </c>
-      <c r="D99" s="34">
+      <c r="D99" s="33">
         <v>750000</v>
       </c>
       <c r="E99" s="6">
@@ -11643,13 +11642,13 @@
         <f t="shared" si="3"/>
         <v>Above Target</v>
       </c>
-      <c r="G99" s="29">
+      <c r="G99" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H99" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>39500</v>
+      <c r="H99" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>47400</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -11659,10 +11658,10 @@
       <c r="B100" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C100" s="34">
+      <c r="C100" s="33">
         <v>390000</v>
       </c>
-      <c r="D100" s="34">
+      <c r="D100" s="33">
         <v>700000</v>
       </c>
       <c r="E100" s="6">
@@ -11673,13 +11672,13 @@
         <f t="shared" si="3"/>
         <v>Below Target</v>
       </c>
-      <c r="G100" s="29">
+      <c r="G100" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>0.8</v>
       </c>
-      <c r="H100" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>19500</v>
+      <c r="H100" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>15600</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -11689,10 +11688,10 @@
       <c r="B101" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C101" s="34">
+      <c r="C101" s="33">
         <v>1600000</v>
       </c>
-      <c r="D101" s="34">
+      <c r="D101" s="33">
         <v>1200000</v>
       </c>
       <c r="E101" s="6">
@@ -11703,13 +11702,13 @@
         <f t="shared" si="3"/>
         <v>Above Target</v>
       </c>
-      <c r="G101" s="29">
+      <c r="G101" s="28">
         <f>IF(Table5[[#This Row],[Performance_Status]]="Below Target",0.8,IF(Table5[[#This Row],[Performance_Status]]="Target Achieved",1,1.2))</f>
         <v>1.2</v>
       </c>
-      <c r="H101" s="31">
-        <f>Table5[[#This Row],[Sales]]*$K$2</f>
-        <v>80000</v>
+      <c r="H101" s="30">
+        <f>Table5[[#This Row],[Sales]]*$K$2*Table5[[#This Row],[Multiplier]]</f>
+        <v>96000</v>
       </c>
     </row>
   </sheetData>
